--- a/api/media/excel_files/predictions/Historical_Data_Donadio_CIA_JD_user1_prediction_results_scenario_Prueba.xlsx
+++ b/api/media/excel_files/predictions/Historical_Data_Donadio_CIA_JD_user1_prediction_results_scenario_Prueba.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="108">
   <si>
     <t>2019-02-01 00:00:00</t>
   </si>
@@ -337,10 +337,7 @@
     <t>actual</t>
   </si>
   <si>
-    <t>arima</t>
-  </si>
-  <si>
-    <t>exp_smooth</t>
+    <t>holt_winters</t>
   </si>
 </sst>
 </file>
@@ -701,7 +698,35 @@
   <dimension ref="A1:BY37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="67" width="24.7109375" customWidth="1"/>
+    <col min="1" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="5" max="15" width="25.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24.7109375" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" customWidth="1"/>
+    <col min="18" max="18" width="24.7109375" customWidth="1"/>
+    <col min="19" max="19" width="25.7109375" customWidth="1"/>
+    <col min="20" max="21" width="24.7109375" customWidth="1"/>
+    <col min="22" max="24" width="25.7109375" customWidth="1"/>
+    <col min="25" max="26" width="24.7109375" customWidth="1"/>
+    <col min="27" max="27" width="25.7109375" customWidth="1"/>
+    <col min="28" max="30" width="24.7109375" customWidth="1"/>
+    <col min="31" max="35" width="25.7109375" customWidth="1"/>
+    <col min="36" max="36" width="24.7109375" customWidth="1"/>
+    <col min="37" max="39" width="25.7109375" customWidth="1"/>
+    <col min="40" max="40" width="23.7109375" customWidth="1"/>
+    <col min="41" max="43" width="24.7109375" customWidth="1"/>
+    <col min="44" max="44" width="25.7109375" customWidth="1"/>
+    <col min="45" max="45" width="24.7109375" customWidth="1"/>
+    <col min="46" max="46" width="25.7109375" customWidth="1"/>
+    <col min="47" max="51" width="24.7109375" customWidth="1"/>
+    <col min="52" max="52" width="23.7109375" customWidth="1"/>
+    <col min="53" max="55" width="24.7109375" customWidth="1"/>
+    <col min="56" max="56" width="25.7109375" customWidth="1"/>
+    <col min="57" max="57" width="24.7109375" customWidth="1"/>
+    <col min="58" max="58" width="25.7109375" customWidth="1"/>
+    <col min="59" max="63" width="24.7109375" customWidth="1"/>
+    <col min="64" max="64" width="23.7109375" customWidth="1"/>
+    <col min="65" max="67" width="24.7109375" customWidth="1"/>
     <col min="68" max="68" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1132,7 +1157,7 @@
         <v>5.316</v>
       </c>
       <c r="BY2">
-        <v>101.61</v>
+        <v>136.42</v>
       </c>
     </row>
     <row r="3" spans="1:77">
@@ -1164,208 +1189,208 @@
         <v>107</v>
       </c>
       <c r="J3">
-        <v>23.0625770630793</v>
+        <v>17.49173188044679</v>
       </c>
       <c r="K3">
-        <v>23.0625770630793</v>
+        <v>8.879135338874452</v>
       </c>
       <c r="L3">
-        <v>23.0625770630793</v>
+        <v>-6.608919684074005</v>
       </c>
       <c r="M3">
-        <v>23.0625770630793</v>
+        <v>-10.18715182417344</v>
       </c>
       <c r="N3">
-        <v>23.0625770630793</v>
+        <v>-2.632829331407542</v>
       </c>
       <c r="O3">
-        <v>23.0625770630793</v>
+        <v>-10.16331565329309</v>
       </c>
       <c r="P3">
-        <v>23.0625770630793</v>
+        <v>17.21308571319526</v>
       </c>
       <c r="Q3">
-        <v>23.0625770630793</v>
+        <v>78.75586977424048</v>
       </c>
       <c r="R3">
-        <v>23.0625770630793</v>
+        <v>11.34171449679664</v>
       </c>
       <c r="S3">
-        <v>23.0625770630793</v>
+        <v>13.79472079569185</v>
       </c>
       <c r="T3">
-        <v>23.0625770630793</v>
+        <v>70.98689400405648</v>
       </c>
       <c r="U3">
-        <v>23.0625770630793</v>
+        <v>9.381755064467681</v>
       </c>
       <c r="V3">
-        <v>23.0625770630793</v>
+        <v>24.14969630025079</v>
       </c>
       <c r="W3">
-        <v>23.0625770630793</v>
+        <v>15.53882157522897</v>
       </c>
       <c r="X3">
-        <v>23.0625770630793</v>
+        <v>0.05393089964094955</v>
       </c>
       <c r="Y3">
-        <v>23.0625770630793</v>
+        <v>-3.523635757006957</v>
       </c>
       <c r="Z3">
-        <v>23.0625770630793</v>
+        <v>4.029016467438748</v>
       </c>
       <c r="AA3">
-        <v>23.0625770630793</v>
+        <v>-3.499975128855784</v>
       </c>
       <c r="AB3">
-        <v>23.0625770630793</v>
+        <v>23.8721020430056</v>
       </c>
       <c r="AC3">
-        <v>23.0625770630793</v>
+        <v>85.42499751250799</v>
       </c>
       <c r="AD3">
-        <v>23.0625770630793</v>
+        <v>18.00003377318609</v>
       </c>
       <c r="AE3">
-        <v>23.0625770630793</v>
+        <v>20.4660175632912</v>
       </c>
       <c r="AF3">
-        <v>23.0625770630793</v>
+        <v>77.63734159143792</v>
       </c>
       <c r="AG3">
-        <v>23.0625770630793</v>
+        <v>16.04145832713971</v>
       </c>
       <c r="AH3">
-        <v>23.0625770630793</v>
+        <v>30.806661639497</v>
       </c>
       <c r="AI3">
-        <v>23.0625770630793</v>
+        <v>22.19750838447316</v>
       </c>
       <c r="AJ3">
-        <v>23.0625770630793</v>
+        <v>6.715781407037365</v>
       </c>
       <c r="AK3">
-        <v>23.0625770630793</v>
+        <v>3.139065336574898</v>
       </c>
       <c r="AL3">
-        <v>23.0625770630793</v>
+        <v>10.69004765638504</v>
       </c>
       <c r="AM3">
-        <v>23.0625770630793</v>
+        <v>3.162939933049</v>
       </c>
       <c r="AN3">
-        <v>23.0625770630793</v>
+        <v>30.5351884189862</v>
       </c>
       <c r="AO3">
-        <v>23.0625770630793</v>
+        <v>92.08505839473936</v>
       </c>
       <c r="AP3">
-        <v>23.0625770630793</v>
+        <v>24.66893097033585</v>
       </c>
       <c r="AQ3">
-        <v>23.0625770630793</v>
+        <v>27.12313212348771</v>
       </c>
       <c r="AR3">
-        <v>23.0625770630793</v>
+        <v>84.30982311391531</v>
       </c>
       <c r="AS3">
-        <v>23.0625770630793</v>
+        <v>22.70595874900412</v>
       </c>
       <c r="AT3">
-        <v>23.0625770630793</v>
+        <v>37.46038563278658</v>
       </c>
       <c r="AU3">
-        <v>23.0625770630793</v>
+        <v>28.85436079107024</v>
       </c>
       <c r="AV3">
-        <v>23.0625770630793</v>
+        <v>13.37980278390233</v>
       </c>
       <c r="AW3">
-        <v>23.0625770630793</v>
+        <v>9.800530032506046</v>
       </c>
       <c r="AX3">
-        <v>23.0625770630793</v>
+        <v>17.35622739187075</v>
       </c>
       <c r="AY3">
-        <v>23.0625770630793</v>
+        <v>9.823839608417703</v>
       </c>
       <c r="AZ3">
-        <v>23.0625770630793</v>
+        <v>37.20089014175043</v>
       </c>
       <c r="BA3">
-        <v>23.0625770630793</v>
+        <v>98.74058974524198</v>
       </c>
       <c r="BB3">
-        <v>23.0625770630793</v>
+        <v>31.32588663548335</v>
       </c>
       <c r="BC3">
-        <v>23.0625770630793</v>
+        <v>33.77908273549416</v>
       </c>
       <c r="BD3">
-        <v>23.0625770630793</v>
+        <v>90.97041786581947</v>
       </c>
       <c r="BE3">
-        <v>23.0625770630793</v>
+        <v>29.36590708623163</v>
       </c>
       <c r="BF3">
-        <v>23.0625770630793</v>
+        <v>44.13779985581366</v>
       </c>
       <c r="BG3">
-        <v>23.0625770630793</v>
+        <v>35.52547284170451</v>
       </c>
       <c r="BH3">
-        <v>23.0625770630793</v>
+        <v>20.03767082007754</v>
       </c>
       <c r="BI3">
-        <v>23.0625770630793</v>
+        <v>16.45932027557003</v>
       </c>
       <c r="BJ3">
-        <v>23.0625770630793</v>
+        <v>24.01355778493587</v>
       </c>
       <c r="BK3">
-        <v>23.0625770630793</v>
+        <v>16.48297230159305</v>
       </c>
       <c r="BL3">
-        <v>23.0625770630793</v>
+        <v>43.86220994183591</v>
       </c>
       <c r="BM3">
-        <v>23.0625770630793</v>
+        <v>98.74058974524198</v>
       </c>
       <c r="BN3">
-        <v>23.0625770630793</v>
+        <v>31.32588663548335</v>
       </c>
       <c r="BO3">
-        <v>23.0625770630793</v>
+        <v>33.77908273549416</v>
       </c>
       <c r="BP3">
-        <v>23.0625770630793</v>
+        <v>90.97041786581947</v>
       </c>
       <c r="BQ3">
-        <v>23.0625770630793</v>
+        <v>29.36590708623163</v>
       </c>
       <c r="BR3">
-        <v>23.0625770630793</v>
+        <v>44.13779985581366</v>
       </c>
       <c r="BS3">
-        <v>23.0625770630793</v>
+        <v>35.52547284170451</v>
       </c>
       <c r="BT3">
-        <v>23.0625770630793</v>
+        <v>20.03767082007754</v>
       </c>
       <c r="BU3">
-        <v>23.0625770630793</v>
+        <v>16.45932027557003</v>
       </c>
       <c r="BV3">
-        <v>23.0625770630793</v>
+        <v>24.01355778493587</v>
       </c>
       <c r="BW3">
-        <v>23.0625770630793</v>
+        <v>16.48297230159305</v>
       </c>
       <c r="BX3">
-        <v>23.0625770630793</v>
+        <v>43.86220994183591</v>
       </c>
       <c r="BY3">
-        <v>101.61</v>
+        <v>136.42</v>
       </c>
     </row>
     <row r="4" spans="1:77">
@@ -1562,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="BY4">
-        <v>97.67</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:77">
@@ -1594,208 +1619,208 @@
         <v>107</v>
       </c>
       <c r="J5">
-        <v>0.06725087035279456</v>
+        <v>0.08596325148998768</v>
       </c>
       <c r="K5">
-        <v>0.06725087035279456</v>
+        <v>0.09802109627114422</v>
       </c>
       <c r="L5">
-        <v>0.06725087035279456</v>
+        <v>0.02572687385657431</v>
       </c>
       <c r="M5">
-        <v>0.06725087035279456</v>
+        <v>0.02573380136201339</v>
       </c>
       <c r="N5">
-        <v>0.06725087035279456</v>
+        <v>0.02572699531068177</v>
       </c>
       <c r="O5">
-        <v>0.06725087035279456</v>
+        <v>0.04980716783111552</v>
       </c>
       <c r="P5">
-        <v>0.06725087035279456</v>
+        <v>0.1341616056859201</v>
       </c>
       <c r="Q5">
-        <v>0.06725087035279456</v>
+        <v>0.01720263883196628</v>
       </c>
       <c r="R5">
-        <v>0.06725087035279456</v>
+        <v>0.3384452164649385</v>
       </c>
       <c r="S5">
-        <v>0.06725087035279456</v>
+        <v>0.1777618280637773</v>
       </c>
       <c r="T5">
-        <v>0.06725087035279456</v>
+        <v>0.1456587618055931</v>
       </c>
       <c r="U5">
-        <v>0.06725087035279456</v>
+        <v>0.01716620863316984</v>
       </c>
       <c r="V5">
-        <v>0.06725087035279456</v>
+        <v>0.06881648522552657</v>
       </c>
       <c r="W5">
-        <v>0.06725087035279456</v>
+        <v>0.08087433098085928</v>
       </c>
       <c r="X5">
-        <v>0.06725087035279456</v>
+        <v>0.008580108821921048</v>
       </c>
       <c r="Y5">
-        <v>0.06725087035279456</v>
+        <v>0.008587036582983751</v>
       </c>
       <c r="Z5">
-        <v>0.06725087035279456</v>
+        <v>0.008580230787275753</v>
       </c>
       <c r="AA5">
-        <v>0.06725087035279456</v>
+        <v>0.03266040356333042</v>
       </c>
       <c r="AB5">
-        <v>0.06725087035279456</v>
+        <v>0.1170148416737761</v>
       </c>
       <c r="AC5">
-        <v>0.06725087035279456</v>
+        <v>5.587435686742193E-05</v>
       </c>
       <c r="AD5">
-        <v>0.06725087035279456</v>
+        <v>0.3212984522454274</v>
       </c>
       <c r="AE5">
-        <v>0.06725087035279456</v>
+        <v>0.1606150784711999</v>
       </c>
       <c r="AF5">
-        <v>0.06725087035279456</v>
+        <v>0.1285120196543318</v>
       </c>
       <c r="AG5">
-        <v>0.06725087035279456</v>
+        <v>1.946098898628068E-05</v>
       </c>
       <c r="AH5">
-        <v>0.06725087035279456</v>
+        <v>0.05166973783697675</v>
       </c>
       <c r="AI5">
-        <v>0.06725087035279456</v>
+        <v>0.06372758169222151</v>
       </c>
       <c r="AJ5">
-        <v>0.06725087035279456</v>
+        <v>-0.008566635899697639</v>
       </c>
       <c r="AK5">
-        <v>0.06725087035279456</v>
+        <v>-0.008559707883011601</v>
       </c>
       <c r="AL5">
-        <v>0.06725087035279456</v>
+        <v>-0.008566513423096285</v>
       </c>
       <c r="AM5">
-        <v>0.06725087035279456</v>
+        <v>0.01551365960857901</v>
       </c>
       <c r="AN5">
-        <v>0.06725087035279456</v>
+        <v>0.09986809797466005</v>
       </c>
       <c r="AO5">
-        <v>0.06725087035279456</v>
+        <v>-0.01709087196089217</v>
       </c>
       <c r="AP5">
-        <v>0.06725087035279456</v>
+        <v>0.3041517061833628</v>
       </c>
       <c r="AQ5">
-        <v>0.06725087035279456</v>
+        <v>0.1434683182934307</v>
       </c>
       <c r="AR5">
-        <v>0.06725087035279456</v>
+        <v>0.1113652525464899</v>
       </c>
       <c r="AS5">
-        <v>0.06725087035279456</v>
+        <v>-0.01712730586321773</v>
       </c>
       <c r="AT5">
-        <v>0.06725087035279456</v>
+        <v>0.03452297124039062</v>
       </c>
       <c r="AU5">
-        <v>0.06725087035279456</v>
+        <v>0.04658081535128993</v>
       </c>
       <c r="AV5">
-        <v>0.06725087035279456</v>
+        <v>-0.02571340629641743</v>
       </c>
       <c r="AW5">
-        <v>0.06725087035279456</v>
+        <v>-0.02570647802410769</v>
       </c>
       <c r="AX5">
-        <v>0.06725087035279456</v>
+        <v>-0.02571328330856867</v>
       </c>
       <c r="AY5">
-        <v>0.06725087035279456</v>
+        <v>-0.00163311002127238</v>
       </c>
       <c r="AZ5">
-        <v>0.06725087035279456</v>
+        <v>0.08272133003755217</v>
       </c>
       <c r="BA5">
-        <v>0.06725087035279456</v>
+        <v>-0.03423763964236334</v>
       </c>
       <c r="BB5">
-        <v>0.06725087035279456</v>
+        <v>0.2870049382470655</v>
       </c>
       <c r="BC5">
-        <v>0.06725087035279456</v>
+        <v>0.1263215548914386</v>
       </c>
       <c r="BD5">
-        <v>0.06725087035279456</v>
+        <v>0.09421849128332413</v>
       </c>
       <c r="BE5">
-        <v>0.06725087035279456</v>
+        <v>-0.03427406546613826</v>
       </c>
       <c r="BF5">
-        <v>0.06725087035279456</v>
+        <v>0.01737621138213079</v>
       </c>
       <c r="BG5">
-        <v>0.06725087035279456</v>
+        <v>0.0294340560076965</v>
       </c>
       <c r="BH5">
-        <v>0.06725087035279456</v>
+        <v>-0.04286016494557697</v>
       </c>
       <c r="BI5">
-        <v>0.06725087035279456</v>
+        <v>-0.04285323705660216</v>
       </c>
       <c r="BJ5">
-        <v>0.06725087035279456</v>
+        <v>-0.04286004272429478</v>
       </c>
       <c r="BK5">
-        <v>0.06725087035279456</v>
+        <v>-0.01877986982032353</v>
       </c>
       <c r="BL5">
-        <v>0.06725087035279456</v>
+        <v>0.06557456877701449</v>
       </c>
       <c r="BM5">
-        <v>0.06725087035279456</v>
+        <v>-0.03423763964236334</v>
       </c>
       <c r="BN5">
-        <v>0.06725087035279456</v>
+        <v>0.2870049382470655</v>
       </c>
       <c r="BO5">
-        <v>0.06725087035279456</v>
+        <v>0.1263215548914386</v>
       </c>
       <c r="BP5">
-        <v>0.06725087035279456</v>
+        <v>0.09421849128332413</v>
       </c>
       <c r="BQ5">
-        <v>0.06725087035279456</v>
+        <v>-0.03427406546613826</v>
       </c>
       <c r="BR5">
-        <v>0.06725087035279456</v>
+        <v>0.01737621138213079</v>
       </c>
       <c r="BS5">
-        <v>0.06725087035279456</v>
+        <v>0.0294340560076965</v>
       </c>
       <c r="BT5">
-        <v>0.06725087035279456</v>
+        <v>-0.04286016494557697</v>
       </c>
       <c r="BU5">
-        <v>0.06725087035279456</v>
+        <v>-0.04285323705660216</v>
       </c>
       <c r="BV5">
-        <v>0.06725087035279456</v>
+        <v>-0.04286004272429478</v>
       </c>
       <c r="BW5">
-        <v>0.06725087035279456</v>
+        <v>-0.01877986982032353</v>
       </c>
       <c r="BX5">
-        <v>0.06725087035279456</v>
+        <v>0.06557456877701449</v>
       </c>
       <c r="BY5">
-        <v>97.67</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:77">
@@ -1992,7 +2017,7 @@
         <v>0.8176</v>
       </c>
       <c r="BY6">
-        <v>85.94</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:77">
@@ -2024,208 +2049,208 @@
         <v>107</v>
       </c>
       <c r="J7">
-        <v>0.5041361258991726</v>
+        <v>0.1899096192021134</v>
       </c>
       <c r="K7">
-        <v>0.5041361258991726</v>
+        <v>0.3373671884282125</v>
       </c>
       <c r="L7">
-        <v>0.5041361258991726</v>
+        <v>0.5271654030703303</v>
       </c>
       <c r="M7">
-        <v>0.5041361258991726</v>
+        <v>1.105329900720926</v>
       </c>
       <c r="N7">
-        <v>0.5041361258991726</v>
+        <v>1.140363278361175</v>
       </c>
       <c r="O7">
-        <v>0.5041361258991726</v>
+        <v>1.241112619767825</v>
       </c>
       <c r="P7">
-        <v>0.5041361258991726</v>
+        <v>1.03815225760611</v>
       </c>
       <c r="Q7">
-        <v>0.5041361258991726</v>
+        <v>1.159283509188938</v>
       </c>
       <c r="R7">
-        <v>0.5041361258991726</v>
+        <v>0.5558510159439654</v>
       </c>
       <c r="S7">
-        <v>0.5041361258991726</v>
+        <v>0.2210152338297068</v>
       </c>
       <c r="T7">
-        <v>0.5041361258991726</v>
+        <v>0.147039041218184</v>
       </c>
       <c r="U7">
-        <v>0.5041361258991726</v>
+        <v>0.1275736030645995</v>
       </c>
       <c r="V7">
-        <v>0.5041361258991726</v>
+        <v>0.0623322250874595</v>
       </c>
       <c r="W7">
-        <v>0.5041361258991726</v>
+        <v>0.209789796127587</v>
       </c>
       <c r="X7">
-        <v>0.5041361258991726</v>
+        <v>0.3995880213730345</v>
       </c>
       <c r="Y7">
-        <v>0.5041361258991726</v>
+        <v>0.977752535718554</v>
       </c>
       <c r="Z7">
-        <v>0.5041361258991726</v>
+        <v>1.012785894026296</v>
       </c>
       <c r="AA7">
-        <v>0.5041361258991726</v>
+        <v>1.113535226021036</v>
       </c>
       <c r="AB7">
-        <v>0.5041361258991726</v>
+        <v>0.910574830081031</v>
       </c>
       <c r="AC7">
-        <v>0.5041361258991726</v>
+        <v>1.031706121854934</v>
       </c>
       <c r="AD7">
-        <v>0.5041361258991726</v>
+        <v>0.4282736270301019</v>
       </c>
       <c r="AE7">
-        <v>0.5041361258991726</v>
+        <v>0.09343782767188258</v>
       </c>
       <c r="AF7">
-        <v>0.5041361258991726</v>
+        <v>0.01946163269729462</v>
       </c>
       <c r="AG7">
-        <v>0.5041361258991726</v>
+        <v>-3.804425466491512E-06</v>
       </c>
       <c r="AH7">
-        <v>0.5041361258991726</v>
+        <v>-0.06524518050155514</v>
       </c>
       <c r="AI7">
-        <v>0.5041361258991726</v>
+        <v>0.08221239252664636</v>
       </c>
       <c r="AJ7">
-        <v>0.5041361258991726</v>
+        <v>0.2720106109708669</v>
       </c>
       <c r="AK7">
-        <v>0.5041361258991726</v>
+        <v>0.8501751098128811</v>
       </c>
       <c r="AL7">
-        <v>0.5041361258991726</v>
+        <v>0.8852084782018157</v>
       </c>
       <c r="AM7">
-        <v>0.5041361258991726</v>
+        <v>0.9859578486471757</v>
       </c>
       <c r="AN7">
-        <v>0.5041361258991726</v>
+        <v>0.7829974693150725</v>
       </c>
       <c r="AO7">
-        <v>0.5041361258991726</v>
+        <v>0.904128722089319</v>
       </c>
       <c r="AP7">
-        <v>0.5041361258991726</v>
+        <v>0.3006962718067017</v>
       </c>
       <c r="AQ7">
-        <v>0.5041361258991726</v>
+        <v>-0.03413952565046635</v>
       </c>
       <c r="AR7">
-        <v>0.5041361258991726</v>
+        <v>-0.1081157188110258</v>
       </c>
       <c r="AS7">
-        <v>0.5041361258991726</v>
+        <v>-0.1275811540327356</v>
       </c>
       <c r="AT7">
-        <v>0.5041361258991726</v>
+        <v>-0.1928225282077729</v>
       </c>
       <c r="AU7">
-        <v>0.5041361258991726</v>
+        <v>-0.04536495327852008</v>
       </c>
       <c r="AV7">
-        <v>0.5041361258991726</v>
+        <v>0.1444332670667517</v>
       </c>
       <c r="AW7">
-        <v>0.5041361258991726</v>
+        <v>0.7225977678098172</v>
       </c>
       <c r="AX7">
-        <v>0.5041361258991726</v>
+        <v>0.7576311215654745</v>
       </c>
       <c r="AY7">
-        <v>0.5041361258991726</v>
+        <v>0.8583804660645953</v>
       </c>
       <c r="AZ7">
-        <v>0.5041361258991726</v>
+        <v>0.6554200791480602</v>
       </c>
       <c r="BA7">
-        <v>0.5041361258991726</v>
+        <v>0.7765513373042693</v>
       </c>
       <c r="BB7">
-        <v>0.5041361258991726</v>
+        <v>0.1731188578530565</v>
       </c>
       <c r="BC7">
-        <v>0.5041361258991726</v>
+        <v>-0.1617169351233883</v>
       </c>
       <c r="BD7">
-        <v>0.5041361258991726</v>
+        <v>-0.2356931287056437</v>
       </c>
       <c r="BE7">
-        <v>0.5041361258991726</v>
+        <v>-0.2551585655384036</v>
       </c>
       <c r="BF7">
-        <v>0.5041361258991726</v>
+        <v>-0.3203999416145487</v>
       </c>
       <c r="BG7">
-        <v>0.5041361258991726</v>
+        <v>-0.1729423695585757</v>
       </c>
       <c r="BH7">
-        <v>0.5041361258991726</v>
+        <v>0.0168558501107052</v>
       </c>
       <c r="BI7">
-        <v>0.5041361258991726</v>
+        <v>0.5950203530059938</v>
       </c>
       <c r="BJ7">
-        <v>0.5041361258991726</v>
+        <v>0.6300537175291967</v>
       </c>
       <c r="BK7">
-        <v>0.5041361258991726</v>
+        <v>0.7308030646156227</v>
       </c>
       <c r="BL7">
-        <v>0.5041361258991726</v>
+        <v>0.5278426835281306</v>
       </c>
       <c r="BM7">
-        <v>0.5041361258991726</v>
+        <v>0.7765513373042693</v>
       </c>
       <c r="BN7">
-        <v>0.5041361258991726</v>
+        <v>0.1731188578530565</v>
       </c>
       <c r="BO7">
-        <v>0.5041361258991726</v>
+        <v>-0.1617169351233883</v>
       </c>
       <c r="BP7">
-        <v>0.5041361258991726</v>
+        <v>-0.2356931287056437</v>
       </c>
       <c r="BQ7">
-        <v>0.5041361258991726</v>
+        <v>-0.2551585655384036</v>
       </c>
       <c r="BR7">
-        <v>0.5041361258991726</v>
+        <v>-0.3203999416145487</v>
       </c>
       <c r="BS7">
-        <v>0.5041361258991726</v>
+        <v>-0.1729423695585757</v>
       </c>
       <c r="BT7">
-        <v>0.5041361258991726</v>
+        <v>0.0168558501107052</v>
       </c>
       <c r="BU7">
-        <v>0.5041361258991726</v>
+        <v>0.5950203530059938</v>
       </c>
       <c r="BV7">
-        <v>0.5041361258991726</v>
+        <v>0.6300537175291967</v>
       </c>
       <c r="BW7">
-        <v>0.5041361258991726</v>
+        <v>0.7308030646156227</v>
       </c>
       <c r="BX7">
-        <v>0.5041361258991726</v>
+        <v>0.5278426835281306</v>
       </c>
       <c r="BY7">
-        <v>85.94</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:77">
@@ -2349,6 +2374,42 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>1.422</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0.711</v>
+      </c>
       <c r="BA8">
         <v>1.7064</v>
       </c>
@@ -2386,7 +2447,7 @@
         <v>1.7775</v>
       </c>
       <c r="BY8">
-        <v>77.15000000000001</v>
+        <v>133.16</v>
       </c>
     </row>
     <row r="9" spans="1:77">
@@ -2415,175 +2476,211 @@
         <v>91</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.6289853594165127</v>
       </c>
       <c r="K9">
-        <v>1.95525</v>
+        <v>1.3755179966898</v>
       </c>
       <c r="L9">
-        <v>1.197834219269103</v>
+        <v>0.8245349668914472</v>
       </c>
       <c r="M9">
-        <v>1.271686856435643</v>
+        <v>1.126684451005144</v>
       </c>
       <c r="N9">
-        <v>0.9882636516931039</v>
+        <v>0.9133975625571493</v>
       </c>
       <c r="O9">
-        <v>0.9347158300809597</v>
+        <v>0.6467578718521527</v>
       </c>
       <c r="P9">
-        <v>1.172057447265754</v>
+        <v>1.108915987982131</v>
       </c>
       <c r="Q9">
-        <v>1.050989063400987</v>
+        <v>0.9881442923987949</v>
       </c>
       <c r="R9">
-        <v>1.007957084688243</v>
+        <v>0.5852533549880956</v>
       </c>
       <c r="S9">
-        <v>0.9440859189787014</v>
+        <v>0.5354272404434263</v>
       </c>
       <c r="T9">
-        <v>1.027192949765407</v>
+        <v>0.7511202774526358</v>
       </c>
       <c r="U9">
-        <v>0.8219616783740069</v>
+        <v>0.3008391246667307</v>
       </c>
       <c r="V9">
-        <v>0.8001833128672956</v>
+        <v>0.3281596715827196</v>
       </c>
       <c r="W9">
-        <v>0.6728810743243592</v>
+        <v>1.074692323933759</v>
       </c>
       <c r="X9">
-        <v>0.8161458499091221</v>
+        <v>0.523709247762862</v>
       </c>
       <c r="Y9">
-        <v>0.7019315812460634</v>
+        <v>0.8258587564894058</v>
       </c>
       <c r="Z9">
-        <v>0.6635315610757767</v>
+        <v>0.6125718545128727</v>
       </c>
       <c r="AA9">
-        <v>0.5395422638986149</v>
+        <v>0.3459321714690622</v>
       </c>
       <c r="AB9">
-        <v>0.4392279781723311</v>
+        <v>0.8080902804275416</v>
       </c>
       <c r="AC9">
-        <v>0.3578985940847935</v>
+        <v>0.6873185607208723</v>
       </c>
       <c r="AD9">
-        <v>0.2918495308603581</v>
+        <v>0.2844276182576209</v>
       </c>
       <c r="AE9">
-        <v>0.2381361818013981</v>
+        <v>0.234601495481889</v>
       </c>
       <c r="AF9">
-        <v>0.1944058528916182</v>
+        <v>0.4502945264849966</v>
       </c>
       <c r="AG9">
-        <v>0.1587707491464687</v>
+        <v>1.335805160201931E-05</v>
       </c>
       <c r="AH9">
-        <v>0.1297107915138478</v>
+        <v>0.02733390945033759</v>
       </c>
       <c r="AI9">
-        <v>0.1059984619571205</v>
+        <v>0.7738665556891327</v>
       </c>
       <c r="AJ9">
-        <v>0.08664015000762031</v>
+        <v>0.2228834818821567</v>
       </c>
       <c r="AK9">
-        <v>0.2654453826790854</v>
+        <v>0.5250329739016659</v>
       </c>
       <c r="AL9">
-        <v>0.4115254230386241</v>
+        <v>0.3117460891215807</v>
       </c>
       <c r="AM9">
-        <v>0.3365204034588234</v>
+        <v>0.04510641903622953</v>
       </c>
       <c r="AN9">
-        <v>0.2752130166279412</v>
+        <v>0.5072645324773278</v>
+      </c>
+      <c r="AO9">
+        <v>0.3864928172533424</v>
+      </c>
+      <c r="AP9">
+        <v>-0.01639809953765711</v>
+      </c>
+      <c r="AQ9">
+        <v>-0.06622421783071294</v>
+      </c>
+      <c r="AR9">
+        <v>0.149468817655041</v>
+      </c>
+      <c r="AS9">
+        <v>-0.3008123462956328</v>
+      </c>
+      <c r="AT9">
+        <v>-0.2734917904142298</v>
+      </c>
+      <c r="AU9">
+        <v>0.4730408603071525</v>
+      </c>
+      <c r="AV9">
+        <v>-0.07794220901709156</v>
+      </c>
+      <c r="AW9">
+        <v>0.2242072874851733</v>
+      </c>
+      <c r="AX9">
+        <v>0.01092039129563012</v>
+      </c>
+      <c r="AY9">
+        <v>-0.2557192901992921</v>
+      </c>
+      <c r="AZ9">
+        <v>0.2064388277244251</v>
       </c>
       <c r="BA9">
-        <v>0.4840593828074725</v>
+        <v>0.08566712757805048</v>
       </c>
       <c r="BB9">
-        <v>0.3959313236336897</v>
+        <v>-0.3172238046433838</v>
       </c>
       <c r="BC9">
-        <v>0.3238653545900555</v>
+        <v>-0.3670499231807857</v>
       </c>
       <c r="BD9">
-        <v>0.2649282478850786</v>
+        <v>-0.1513568886818774</v>
       </c>
       <c r="BE9">
-        <v>0.2167243457267168</v>
+        <v>-0.601638050405233</v>
       </c>
       <c r="BF9">
-        <v>0.1772964095062385</v>
+        <v>-0.5743174990063041</v>
       </c>
       <c r="BG9">
-        <v>0.1450449645654222</v>
+        <v>0.1722151476396333</v>
       </c>
       <c r="BH9">
-        <v>0.11866262214422</v>
+        <v>-0.3787679146356628</v>
       </c>
       <c r="BI9">
-        <v>0.09708055160862325</v>
+        <v>-0.0766184192948656</v>
       </c>
       <c r="BJ9">
-        <v>0.07942482454607737</v>
+        <v>-0.2899053121434225</v>
       </c>
       <c r="BK9">
-        <v>0.06498078958110871</v>
+        <v>-0.5565449934755877</v>
       </c>
       <c r="BL9">
-        <v>0.1824598415560001</v>
+        <v>-0.09438687936242846</v>
       </c>
       <c r="BM9">
-        <v>0.1661685816210555</v>
+        <v>0.08566712757805048</v>
       </c>
       <c r="BN9">
-        <v>0.1661685816210555</v>
+        <v>-0.3172238046433838</v>
       </c>
       <c r="BO9">
-        <v>0.1661685816210555</v>
+        <v>-0.3670499231807857</v>
       </c>
       <c r="BP9">
-        <v>0.1661685816210555</v>
+        <v>-0.1513568886818774</v>
       </c>
       <c r="BQ9">
-        <v>0.1661685816210555</v>
+        <v>-0.601638050405233</v>
       </c>
       <c r="BR9">
-        <v>0.1661685816210555</v>
+        <v>-0.5743174990063041</v>
       </c>
       <c r="BS9">
-        <v>0.1661685816210555</v>
+        <v>0.1722151476396333</v>
       </c>
       <c r="BT9">
-        <v>0.1661685816210555</v>
+        <v>-0.3787679146356628</v>
       </c>
       <c r="BU9">
-        <v>0.1661685816210555</v>
+        <v>-0.0766184192948656</v>
       </c>
       <c r="BV9">
-        <v>0.1661685816210555</v>
+        <v>-0.2899053121434225</v>
       </c>
       <c r="BW9">
-        <v>0.1661685816210555</v>
+        <v>-0.5565449934755877</v>
       </c>
       <c r="BX9">
-        <v>0.1661685816210555</v>
+        <v>-0.09438687936242846</v>
       </c>
       <c r="BY9">
-        <v>77.15000000000001</v>
+        <v>133.16</v>
       </c>
     </row>
     <row r="10" spans="1:77">
@@ -2707,6 +2804,42 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0.771</v>
+      </c>
+      <c r="AU10">
+        <v>0.07709999999999999</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>1.0794</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0.07709999999999999</v>
+      </c>
       <c r="BA10">
         <v>0</v>
       </c>
@@ -2744,7 +2877,7 @@
         <v>1.542</v>
       </c>
       <c r="BY10">
-        <v>92.59</v>
+        <v>126.16</v>
       </c>
     </row>
     <row r="11" spans="1:77">
@@ -2773,175 +2906,211 @@
         <v>92</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.1283963262024389</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>-0.04502852605806183</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>-0.06429527638186297</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>0.03211014968668015</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>0.2054886495846162</v>
       </c>
       <c r="O11">
-        <v>0.2202808649162984</v>
+        <v>0.1476841330618218</v>
       </c>
       <c r="P11">
-        <v>0.1672020253666265</v>
+        <v>-0.04501360517547749</v>
       </c>
       <c r="Q11">
-        <v>0.1291627588035782</v>
+        <v>0.008559935041983241</v>
       </c>
       <c r="R11">
-        <v>0.1010614624439983</v>
+        <v>0.2913774337371571</v>
       </c>
       <c r="S11">
-        <v>0.07983287921465151</v>
+        <v>-0.04285281841056101</v>
       </c>
       <c r="T11">
-        <v>0.06352402005710429</v>
+        <v>-0.04285169347092413</v>
       </c>
       <c r="U11">
-        <v>0.05083203711155376</v>
+        <v>-0.0428287888779474</v>
       </c>
       <c r="V11">
-        <v>0.04085527125970032</v>
+        <v>0.1712546798012193</v>
       </c>
       <c r="W11">
-        <v>0.0329508648926536</v>
+        <v>-0.002170173097920503</v>
       </c>
       <c r="X11">
-        <v>0.0266491975573741</v>
+        <v>-0.0214369240603608</v>
       </c>
       <c r="Y11">
-        <v>0.02160028064116461</v>
+        <v>0.07496850136954308</v>
       </c>
       <c r="Z11">
-        <v>0.01753895375310987</v>
+        <v>0.2483470006288398</v>
       </c>
       <c r="AA11">
-        <v>0.01426157754881129</v>
+        <v>0.190542483467407</v>
       </c>
       <c r="AB11">
-        <v>0.01160999664243054</v>
+        <v>-0.002155268046207082</v>
       </c>
       <c r="AC11">
-        <v>0.03801258875044296</v>
+        <v>0.05141827153261445</v>
       </c>
       <c r="AD11">
-        <v>0.2159688066423176</v>
+        <v>0.334235771886908</v>
       </c>
       <c r="AE11">
-        <v>0.1762209000315774</v>
+        <v>5.534035985174657E-06</v>
       </c>
       <c r="AF11">
-        <v>0.1438604335923147</v>
+        <v>6.658336982864888E-06</v>
       </c>
       <c r="AG11">
-        <v>0.1174904380410884</v>
+        <v>2.956229132040911E-05</v>
       </c>
       <c r="AH11">
-        <v>0.09598605407825667</v>
+        <v>0.2141130303318477</v>
       </c>
       <c r="AI11">
-        <v>0.0784389177098036</v>
+        <v>0.04068817679406891</v>
       </c>
       <c r="AJ11">
-        <v>0.06411375666528007</v>
+        <v>0.02142142519298947</v>
       </c>
       <c r="AK11">
-        <v>0.1227604519220758</v>
+        <v>0.1178268499842541</v>
       </c>
       <c r="AL11">
-        <v>0.1003738987663028</v>
+        <v>0.2912053543493093</v>
       </c>
       <c r="AM11">
-        <v>0.08207965539567907</v>
+        <v>0.2334008365492373</v>
       </c>
       <c r="AN11">
-        <v>0.06712635945116102</v>
+        <v>0.0407030843969842</v>
+      </c>
+      <c r="AO11">
+        <v>0.0942766233371666</v>
+      </c>
+      <c r="AP11">
+        <v>0.3770941207550622</v>
+      </c>
+      <c r="AQ11">
+        <v>0.0428638673300656</v>
+      </c>
+      <c r="AR11">
+        <v>0.04286499099242411</v>
+      </c>
+      <c r="AS11">
+        <v>0.04288789430812244</v>
+      </c>
+      <c r="AT11">
+        <v>0.2569713617100104</v>
+      </c>
+      <c r="AU11">
+        <v>0.08354651902238806</v>
+      </c>
+      <c r="AV11">
+        <v>0.06427976793154901</v>
+      </c>
+      <c r="AW11">
+        <v>0.1606851920841747</v>
+      </c>
+      <c r="AX11">
+        <v>0.3340636900661924</v>
+      </c>
+      <c r="AY11">
+        <v>0.2762591877117951</v>
+      </c>
+      <c r="AZ11">
+        <v>0.08356143492090291</v>
       </c>
       <c r="BA11">
-        <v>0.05490168612515788</v>
+        <v>0.1371349743713257</v>
       </c>
       <c r="BB11">
-        <v>0.04490626156481472</v>
+        <v>0.4199524731940523</v>
       </c>
       <c r="BC11">
-        <v>0.03673258834771564</v>
+        <v>0.08572222538819639</v>
       </c>
       <c r="BD11">
-        <v>0.03004798177181429</v>
+        <v>0.08572334968927645</v>
       </c>
       <c r="BE11">
-        <v>0.02458072795895142</v>
+        <v>0.08574625364371311</v>
       </c>
       <c r="BF11">
-        <v>0.1603742926048006</v>
+        <v>0.2998297216846811</v>
       </c>
       <c r="BG11">
-        <v>0.1452261219768181</v>
+        <v>0.1264048713374348</v>
       </c>
       <c r="BH11">
-        <v>0.1188108286919034</v>
+        <v>0.1071381203426564</v>
       </c>
       <c r="BI11">
-        <v>0.09720180270809435</v>
+        <v>0.2035435454531252</v>
       </c>
       <c r="BJ11">
-        <v>0.2758310235495848</v>
+        <v>0.3769220458295398</v>
       </c>
       <c r="BK11">
-        <v>0.2256689618598928</v>
+        <v>0.319117532368765</v>
       </c>
       <c r="BL11">
-        <v>0.198651590687793</v>
+        <v>0.1264197836944558</v>
       </c>
       <c r="BM11">
-        <v>0.1546003492673272</v>
+        <v>0.1371349743713257</v>
       </c>
       <c r="BN11">
-        <v>0.1546003492673272</v>
+        <v>0.4199524731940523</v>
       </c>
       <c r="BO11">
-        <v>0.1546003492673272</v>
+        <v>0.08572222538819639</v>
       </c>
       <c r="BP11">
-        <v>0.1546003492673272</v>
+        <v>0.08572334968927645</v>
       </c>
       <c r="BQ11">
-        <v>0.1546003492673272</v>
+        <v>0.08574625364371311</v>
       </c>
       <c r="BR11">
-        <v>0.1546003492673272</v>
+        <v>0.2998297216846811</v>
       </c>
       <c r="BS11">
-        <v>0.1546003492673272</v>
+        <v>0.1264048713374348</v>
       </c>
       <c r="BT11">
-        <v>0.1546003492673272</v>
+        <v>0.1071381203426564</v>
       </c>
       <c r="BU11">
-        <v>0.1546003492673272</v>
+        <v>0.2035435454531252</v>
       </c>
       <c r="BV11">
-        <v>0.1546003492673272</v>
+        <v>0.3769220458295398</v>
       </c>
       <c r="BW11">
-        <v>0.1546003492673272</v>
+        <v>0.319117532368765</v>
       </c>
       <c r="BX11">
-        <v>0.1546003492673272</v>
+        <v>0.1264197836944558</v>
       </c>
       <c r="BY11">
-        <v>92.59</v>
+        <v>126.16</v>
       </c>
     </row>
     <row r="12" spans="1:77">
@@ -3170,205 +3339,205 @@
         <v>107</v>
       </c>
       <c r="J13">
-        <v>0.03108799792916942</v>
+        <v>0.003208100292387675</v>
       </c>
       <c r="K13">
-        <v>0.03108799792916942</v>
+        <v>0.003209784377767748</v>
       </c>
       <c r="L13">
-        <v>0.03108799792916942</v>
+        <v>0.02706446163290809</v>
       </c>
       <c r="M13">
-        <v>0.03108799792916942</v>
+        <v>0.003204475994652178</v>
       </c>
       <c r="N13">
-        <v>0.03108799792916942</v>
+        <v>0.003190086879084453</v>
       </c>
       <c r="O13">
-        <v>0.03108799792916942</v>
+        <v>0.003169828893924372</v>
       </c>
       <c r="P13">
-        <v>0.03108799792916942</v>
+        <v>0.02703688558881873</v>
       </c>
       <c r="Q13">
-        <v>0.03108799792916942</v>
+        <v>0.1294355780515292</v>
       </c>
       <c r="R13">
-        <v>0.03108799792916942</v>
+        <v>0.002087273189912815</v>
       </c>
       <c r="S13">
-        <v>0.03108799792916942</v>
+        <v>0.002299198805526405</v>
       </c>
       <c r="T13">
-        <v>0.03108799792916942</v>
+        <v>0.1931670935038949</v>
       </c>
       <c r="U13">
-        <v>0.03108799792916942</v>
+        <v>0.0655677262574057</v>
       </c>
       <c r="V13">
-        <v>0.03108799792916942</v>
+        <v>0.001085751171520079</v>
       </c>
       <c r="W13">
-        <v>0.03108799792916942</v>
+        <v>0.001087435288525604</v>
       </c>
       <c r="X13">
-        <v>0.03108799792916942</v>
+        <v>0.0249421125752914</v>
       </c>
       <c r="Y13">
-        <v>0.03108799792916942</v>
+        <v>0.001082125545600027</v>
       </c>
       <c r="Z13">
-        <v>0.03108799792916942</v>
+        <v>0.001067736461657753</v>
       </c>
       <c r="AA13">
-        <v>0.03108799792916942</v>
+        <v>0.001047478508123124</v>
       </c>
       <c r="AB13">
-        <v>0.03108799792916942</v>
+        <v>0.02491453523464293</v>
       </c>
       <c r="AC13">
-        <v>0.03108799792916942</v>
+        <v>0.127313226305918</v>
       </c>
       <c r="AD13">
-        <v>0.03108799792916942</v>
+        <v>-3.507852407298728E-05</v>
       </c>
       <c r="AE13">
-        <v>0.03108799792916942</v>
+        <v>0.0001768471231660546</v>
       </c>
       <c r="AF13">
-        <v>0.03108799792916942</v>
+        <v>0.19104474185316</v>
       </c>
       <c r="AG13">
-        <v>0.03108799792916942</v>
+        <v>0.06344538317666173</v>
       </c>
       <c r="AH13">
-        <v>0.03108799792916942</v>
+        <v>-0.001036594723720259</v>
       </c>
       <c r="AI13">
-        <v>0.03108799792916942</v>
+        <v>-0.001034910575089289</v>
       </c>
       <c r="AJ13">
-        <v>0.03108799792916942</v>
+        <v>0.02281976674330195</v>
       </c>
       <c r="AK13">
-        <v>0.03108799792916942</v>
+        <v>-0.001040220254763975</v>
       </c>
       <c r="AL13">
-        <v>0.03108799792916942</v>
+        <v>-0.001054609307080803</v>
       </c>
       <c r="AM13">
-        <v>0.03108799792916942</v>
+        <v>-0.001074867228989987</v>
       </c>
       <c r="AN13">
-        <v>0.03108799792916942</v>
+        <v>0.02279218952915527</v>
       </c>
       <c r="AO13">
-        <v>0.03108799792916942</v>
+        <v>0.1251908806320557</v>
       </c>
       <c r="AP13">
-        <v>0.03108799792916942</v>
+        <v>-0.0021574184740661</v>
       </c>
       <c r="AQ13">
-        <v>0.03108799792916942</v>
+        <v>-0.001945492795201613</v>
       </c>
       <c r="AR13">
-        <v>0.03108799792916942</v>
+        <v>0.1889224019664178</v>
       </c>
       <c r="AS13">
-        <v>0.03108799792916942</v>
+        <v>0.06132303478317948</v>
       </c>
       <c r="AT13">
-        <v>0.03108799792916942</v>
+        <v>-0.003158943085577071</v>
       </c>
       <c r="AU13">
-        <v>0.03108799792916942</v>
+        <v>-0.003157258905320648</v>
       </c>
       <c r="AV13">
-        <v>0.03108799792916942</v>
+        <v>0.02069741844469605</v>
       </c>
       <c r="AW13">
-        <v>0.03108799792916942</v>
+        <v>-0.00316256852174443</v>
       </c>
       <c r="AX13">
-        <v>0.03108799792916942</v>
+        <v>-0.003176957542435806</v>
       </c>
       <c r="AY13">
-        <v>0.03108799792916942</v>
+        <v>-0.003197215432719537</v>
       </c>
       <c r="AZ13">
-        <v>0.03108799792916942</v>
+        <v>0.02066984135705117</v>
       </c>
       <c r="BA13">
-        <v>0.03108799792916942</v>
+        <v>0.1230685324915771</v>
       </c>
       <c r="BB13">
-        <v>0.03108799792916942</v>
+        <v>-0.004279770441298895</v>
       </c>
       <c r="BC13">
-        <v>0.03108799792916942</v>
+        <v>-0.004067844794582508</v>
       </c>
       <c r="BD13">
-        <v>0.03108799792916942</v>
+        <v>0.1868000499380467</v>
       </c>
       <c r="BE13">
-        <v>0.03108799792916942</v>
+        <v>0.05920068556997156</v>
       </c>
       <c r="BF13">
-        <v>0.03108799792916942</v>
+        <v>-0.00528129138500057</v>
       </c>
       <c r="BG13">
-        <v>0.03108799792916942</v>
+        <v>-0.005279607251816074</v>
       </c>
       <c r="BH13">
-        <v>0.03108799792916942</v>
+        <v>0.01857507005115379</v>
       </c>
       <c r="BI13">
-        <v>0.03108799792916942</v>
+        <v>-0.005284916606871123</v>
       </c>
       <c r="BJ13">
-        <v>0.03108799792916942</v>
+        <v>-0.005299305674688448</v>
       </c>
       <c r="BK13">
-        <v>0.03108799792916942</v>
+        <v>-0.005319563612312537</v>
       </c>
       <c r="BL13">
-        <v>0.03108799792916942</v>
+        <v>0.01854749312981594</v>
       </c>
       <c r="BM13">
-        <v>0.03108799792916942</v>
+        <v>0.1230685324915771</v>
       </c>
       <c r="BN13">
-        <v>0.03108799792916942</v>
+        <v>-0.004279770441298895</v>
       </c>
       <c r="BO13">
-        <v>0.03108799792916942</v>
+        <v>-0.004067844794582508</v>
       </c>
       <c r="BP13">
-        <v>0.03108799792916942</v>
+        <v>0.1868000499380467</v>
       </c>
       <c r="BQ13">
-        <v>0.03108799792916942</v>
+        <v>0.05920068556997156</v>
       </c>
       <c r="BR13">
-        <v>0.03108799792916942</v>
+        <v>-0.00528129138500057</v>
       </c>
       <c r="BS13">
-        <v>0.03108799792916942</v>
+        <v>-0.005279607251816074</v>
       </c>
       <c r="BT13">
-        <v>0.03108799792916942</v>
+        <v>0.01857507005115379</v>
       </c>
       <c r="BU13">
-        <v>0.03108799792916942</v>
+        <v>-0.005284916606871123</v>
       </c>
       <c r="BV13">
-        <v>0.03108799792916942</v>
+        <v>-0.005299305674688448</v>
       </c>
       <c r="BW13">
-        <v>0.03108799792916942</v>
+        <v>-0.005319563612312537</v>
       </c>
       <c r="BX13">
-        <v>0.03108799792916942</v>
+        <v>0.01854749312981594</v>
       </c>
       <c r="BY13">
         <v>100</v>
@@ -3600,205 +3769,205 @@
         <v>107</v>
       </c>
       <c r="J15">
-        <v>0.0007124841250260975</v>
+        <v>-0.000536328272571578</v>
       </c>
       <c r="K15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0005233554880188446</v>
       </c>
       <c r="L15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0005104268300595951</v>
       </c>
       <c r="M15">
-        <v>0.0007124841250260975</v>
+        <v>-0.000497542301256818</v>
       </c>
       <c r="N15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0004847019144500965</v>
       </c>
       <c r="O15">
-        <v>0.0007124841250260975</v>
+        <v>0.007201780224040972</v>
       </c>
       <c r="P15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0005030394736225718</v>
       </c>
       <c r="Q15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0003734490684363594</v>
       </c>
       <c r="R15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0003585363762710371</v>
       </c>
       <c r="S15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0003436966300360186</v>
       </c>
       <c r="T15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0003289297263284057</v>
       </c>
       <c r="U15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0004271508666140909</v>
       </c>
       <c r="V15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0002044679571642666</v>
       </c>
       <c r="W15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0001931103003296142</v>
       </c>
       <c r="X15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0001817890731111726</v>
       </c>
       <c r="Y15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0001705043147185678</v>
       </c>
       <c r="Z15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0001592560744626813</v>
       </c>
       <c r="AA15">
-        <v>0.0007124841250260975</v>
+        <v>0.007524998615045908</v>
       </c>
       <c r="AB15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0001807483988334146</v>
       </c>
       <c r="AC15">
-        <v>0.0007124841250260975</v>
+        <v>-5.273731071236195E-05</v>
       </c>
       <c r="AD15">
-        <v>0.0007124841250260975</v>
+        <v>-3.938680433464303E-05</v>
       </c>
       <c r="AE15">
-        <v>0.0007124841250260975</v>
+        <v>-2.610179654411685E-05</v>
       </c>
       <c r="AF15">
-        <v>0.0007124841250260975</v>
+        <v>-1.288221940510626E-05</v>
       </c>
       <c r="AG15">
-        <v>0.0007124841250260975</v>
+        <v>-0.0001126338498055412</v>
       </c>
       <c r="AH15">
-        <v>0.0007124841250260975</v>
+        <v>0.0001084989740493702</v>
       </c>
       <c r="AI15">
-        <v>0.0007124841250260975</v>
+        <v>0.0001183316351516541</v>
       </c>
       <c r="AJ15">
-        <v>0.0007124841250260975</v>
+        <v>0.0001281351338243241</v>
       </c>
       <c r="AK15">
-        <v>0.0007124841250260975</v>
+        <v>0.0001379093962605315</v>
       </c>
       <c r="AL15">
-        <v>0.0007124841250260975</v>
+        <v>0.0001476543387177402</v>
       </c>
       <c r="AM15">
-        <v>0.0007124841250260975</v>
+        <v>0.007829770058184674</v>
       </c>
       <c r="AN15">
-        <v>0.0007124841250260975</v>
+        <v>0.0002731245683052705</v>
       </c>
       <c r="AO15">
-        <v>0.0007124841250260975</v>
+        <v>0.000398929735531626</v>
       </c>
       <c r="AP15">
-        <v>0.0007124841250260975</v>
+        <v>0.000410094434198223</v>
       </c>
       <c r="AQ15">
-        <v>0.0007124841250260975</v>
+        <v>0.000421204050141028</v>
       </c>
       <c r="AR15">
-        <v>0.0007124841250260975</v>
+        <v>0.0004322586016980831</v>
       </c>
       <c r="AS15">
-        <v>0.0007124841250260975</v>
+        <v>0.0003303617217037346</v>
       </c>
       <c r="AT15">
-        <v>0.0007124841250260975</v>
+        <v>0.0005493326290756707</v>
       </c>
       <c r="AU15">
-        <v>0.0007124841250260975</v>
+        <v>0.0005570313744614511</v>
       </c>
       <c r="AV15">
-        <v>0.0007124841250260975</v>
+        <v>0.0005647111231423777</v>
       </c>
       <c r="AW15">
-        <v>0.0007124841250260975</v>
+        <v>0.0005723717529170843</v>
       </c>
       <c r="AX15">
-        <v>0.0007124841250260975</v>
+        <v>0.0005800131318797595</v>
       </c>
       <c r="AY15">
-        <v>0.0007124841250260975</v>
+        <v>0.008261977093929456</v>
       </c>
       <c r="AZ15">
-        <v>0.0007124841250260975</v>
+        <v>0.0005513470350230061</v>
       </c>
       <c r="BA15">
-        <v>0.0007124841250260975</v>
+        <v>0.0006757831053874077</v>
       </c>
       <c r="BB15">
-        <v>0.0007124841250260975</v>
+        <v>0.0006888793569975259</v>
       </c>
       <c r="BC15">
-        <v>0.0007124841250260975</v>
+        <v>0.0007019749829530671</v>
       </c>
       <c r="BD15">
-        <v>0.0007124841250260975</v>
+        <v>0.0007150697391446161</v>
       </c>
       <c r="BE15">
-        <v>0.0007124841250260975</v>
+        <v>0.0006152764543134556</v>
       </c>
       <c r="BF15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008358290276969001</v>
       </c>
       <c r="BG15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008461915640307815</v>
       </c>
       <c r="BH15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008565727831061442</v>
       </c>
       <c r="BI15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008669724740383769</v>
       </c>
       <c r="BJ15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008773904156363254</v>
       </c>
       <c r="BK15">
-        <v>0.0007124841250260975</v>
+        <v>0.008561525406906566</v>
       </c>
       <c r="BL15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008917392188017961</v>
       </c>
       <c r="BM15">
-        <v>0.0007124841250260975</v>
+        <v>0.0006757831053874077</v>
       </c>
       <c r="BN15">
-        <v>0.0007124841250260975</v>
+        <v>0.0006888793569975259</v>
       </c>
       <c r="BO15">
-        <v>0.0007124841250260975</v>
+        <v>0.0007019749829530671</v>
       </c>
       <c r="BP15">
-        <v>0.0007124841250260975</v>
+        <v>0.0007150697391446161</v>
       </c>
       <c r="BQ15">
-        <v>0.0007124841250260975</v>
+        <v>0.0006152764543134556</v>
       </c>
       <c r="BR15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008358290276969001</v>
       </c>
       <c r="BS15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008461915640307815</v>
       </c>
       <c r="BT15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008565727831061442</v>
       </c>
       <c r="BU15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008669724740383769</v>
       </c>
       <c r="BV15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008773904156363254</v>
       </c>
       <c r="BW15">
-        <v>0.0007124841250260975</v>
+        <v>0.008561525406906566</v>
       </c>
       <c r="BX15">
-        <v>0.0007124841250260975</v>
+        <v>0.0008917392188017961</v>
       </c>
       <c r="BY15">
         <v>100</v>
@@ -3998,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="BY16">
-        <v>82.18000000000001</v>
+        <v>151.64</v>
       </c>
     </row>
     <row r="17" spans="1:77">
@@ -4030,208 +4199,208 @@
         <v>107</v>
       </c>
       <c r="J17">
-        <v>0.009703077590818046</v>
+        <v>0.01671257906878579</v>
       </c>
       <c r="K17">
-        <v>0.009703077590818046</v>
+        <v>0.01193313008742659</v>
       </c>
       <c r="L17">
-        <v>0.009703077590818046</v>
+        <v>0.007469401888878338</v>
       </c>
       <c r="M17">
-        <v>0.009703077590818046</v>
+        <v>0.03983654770162644</v>
       </c>
       <c r="N17">
-        <v>0.009703077590818046</v>
+        <v>0.01790126416935257</v>
       </c>
       <c r="O17">
-        <v>0.009703077590818046</v>
+        <v>0.01396351827746487</v>
       </c>
       <c r="P17">
-        <v>0.009703077590818046</v>
+        <v>0.06929178946085146</v>
       </c>
       <c r="Q17">
-        <v>0.009703077590818046</v>
+        <v>0.01328592345894734</v>
       </c>
       <c r="R17">
-        <v>0.009703077590818046</v>
+        <v>0.009895805667794553</v>
       </c>
       <c r="S17">
-        <v>0.009703077590818046</v>
+        <v>0.006625452486028194</v>
       </c>
       <c r="T17">
-        <v>0.009703077590818046</v>
+        <v>0.003540464187300401</v>
       </c>
       <c r="U17">
-        <v>0.009703077590818046</v>
+        <v>0.01281791405650164</v>
       </c>
       <c r="V17">
-        <v>0.009703077590818046</v>
+        <v>-0.009384945292745594</v>
       </c>
       <c r="W17">
-        <v>0.009703077590818046</v>
+        <v>-0.01005529576849423</v>
       </c>
       <c r="X17">
-        <v>0.009703077590818046</v>
+        <v>-0.01054204355252378</v>
       </c>
       <c r="Y17">
-        <v>0.009703077590818046</v>
+        <v>0.02560487986741378</v>
       </c>
       <c r="Z17">
-        <v>0.009703077590818046</v>
+        <v>-0.0170206549368942</v>
       </c>
       <c r="AA17">
-        <v>0.009703077590818046</v>
+        <v>-0.01675270654047726</v>
       </c>
       <c r="AB17">
-        <v>0.009703077590818046</v>
+        <v>0.04282012805810417</v>
       </c>
       <c r="AC17">
-        <v>0.009703077590818046</v>
+        <v>-0.02009943611943116</v>
       </c>
       <c r="AD17">
-        <v>0.009703077590818046</v>
+        <v>-0.01899824315541419</v>
       </c>
       <c r="AE17">
-        <v>0.009703077590818046</v>
+        <v>-0.01781864046229885</v>
       </c>
       <c r="AF17">
-        <v>0.009703077590818046</v>
+        <v>-0.01658335698234175</v>
       </c>
       <c r="AG17">
-        <v>0.009703077590818046</v>
+        <v>-0.003188037258585726</v>
       </c>
       <c r="AH17">
-        <v>0.009703077590818046</v>
+        <v>-0.02153326650074353</v>
       </c>
       <c r="AI17">
-        <v>0.009703077590818046</v>
+        <v>-0.01865012481710723</v>
       </c>
       <c r="AJ17">
-        <v>0.009703077590818046</v>
+        <v>-0.01591857597512083</v>
       </c>
       <c r="AK17">
-        <v>0.009703077590818046</v>
+        <v>0.02309202033064906</v>
       </c>
       <c r="AL17">
-        <v>0.009703077590818046</v>
+        <v>-0.01703354559591136</v>
       </c>
       <c r="AM17">
-        <v>0.009703077590818046</v>
+        <v>-0.01462937891048429</v>
       </c>
       <c r="AN17">
-        <v>0.009703077590818046</v>
+        <v>0.04672359607498051</v>
       </c>
       <c r="AO17">
-        <v>0.009703077590818046</v>
+        <v>-0.01475780035850368</v>
       </c>
       <c r="AP17">
-        <v>0.009703077590818046</v>
+        <v>-0.01254111018623402</v>
       </c>
       <c r="AQ17">
-        <v>0.009703077590818046</v>
+        <v>-0.01054534784228834</v>
       </c>
       <c r="AR17">
-        <v>0.009703077590818046</v>
+        <v>-0.008766960081420598</v>
       </c>
       <c r="AS17">
-        <v>0.009703077590818046</v>
+        <v>0.004926653258947046</v>
       </c>
       <c r="AT17">
-        <v>0.009703077590818046</v>
+        <v>-0.007280420521063504</v>
       </c>
       <c r="AU17">
-        <v>0.009703077590818046</v>
+        <v>-0.00474079995955464</v>
       </c>
       <c r="AV17">
-        <v>0.009703077590818046</v>
+        <v>-0.002597666515949342</v>
       </c>
       <c r="AW17">
-        <v>0.009703077590818046</v>
+        <v>0.035627755486386</v>
       </c>
       <c r="AX17">
-        <v>0.009703077590818046</v>
+        <v>-0.005434445520419891</v>
       </c>
       <c r="AY17">
-        <v>0.009703077590818046</v>
+        <v>-0.004076461113292925</v>
       </c>
       <c r="AZ17">
-        <v>0.009703077590818046</v>
+        <v>0.05615891757410874</v>
       </c>
       <c r="BA17">
-        <v>0.009703077590818046</v>
+        <v>0.02178090514470768</v>
       </c>
       <c r="BB17">
-        <v>0.009703077590818046</v>
+        <v>0.02534649416476394</v>
       </c>
       <c r="BC17">
-        <v>0.009703077590818046</v>
+        <v>0.02874802560833312</v>
       </c>
       <c r="BD17">
-        <v>0.009703077590818046</v>
+        <v>0.03199919861114371</v>
       </c>
       <c r="BE17">
-        <v>0.009703077590818046</v>
+        <v>0.04723866769709484</v>
       </c>
       <c r="BF17">
-        <v>0.009703077590818046</v>
+        <v>0.03262050382773708</v>
       </c>
       <c r="BG17">
-        <v>0.009703077590818046</v>
+        <v>0.03610287403721563</v>
       </c>
       <c r="BH17">
-        <v>0.009703077590818046</v>
+        <v>0.03945803714138797</v>
       </c>
       <c r="BI17">
-        <v>0.009703077590818046</v>
+        <v>0.079152475939018</v>
       </c>
       <c r="BJ17">
-        <v>0.009703077590818046</v>
+        <v>0.04588075160633287</v>
       </c>
       <c r="BK17">
-        <v>0.009703077590818046</v>
+        <v>0.04893486437972914</v>
       </c>
       <c r="BL17">
-        <v>0.009703077590818046</v>
+        <v>0.1109776775400463</v>
       </c>
       <c r="BM17">
-        <v>0.009703077590818046</v>
+        <v>0.02178090514470768</v>
       </c>
       <c r="BN17">
-        <v>0.009703077590818046</v>
+        <v>0.02534649416476394</v>
       </c>
       <c r="BO17">
-        <v>0.009703077590818046</v>
+        <v>0.02874802560833312</v>
       </c>
       <c r="BP17">
-        <v>0.009703077590818046</v>
+        <v>0.03199919861114371</v>
       </c>
       <c r="BQ17">
-        <v>0.009703077590818046</v>
+        <v>0.04723866769709484</v>
       </c>
       <c r="BR17">
-        <v>0.009703077590818046</v>
+        <v>0.03262050382773708</v>
       </c>
       <c r="BS17">
-        <v>0.009703077590818046</v>
+        <v>0.03610287403721563</v>
       </c>
       <c r="BT17">
-        <v>0.009703077590818046</v>
+        <v>0.03945803714138797</v>
       </c>
       <c r="BU17">
-        <v>0.009703077590818046</v>
+        <v>0.079152475939018</v>
       </c>
       <c r="BV17">
-        <v>0.009703077590818046</v>
+        <v>0.04588075160633287</v>
       </c>
       <c r="BW17">
-        <v>0.009703077590818046</v>
+        <v>0.04893486437972914</v>
       </c>
       <c r="BX17">
-        <v>0.009703077590818046</v>
+        <v>0.1109776775400463</v>
       </c>
       <c r="BY17">
-        <v>82.18000000000001</v>
+        <v>151.64</v>
       </c>
     </row>
     <row r="18" spans="1:77">
@@ -4428,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="BY18">
-        <v>82.63</v>
+        <v>135.43</v>
       </c>
     </row>
     <row r="19" spans="1:77">
@@ -4460,208 +4629,208 @@
         <v>107</v>
       </c>
       <c r="J19">
-        <v>0.06749504388556039</v>
+        <v>0.05693971970541348</v>
       </c>
       <c r="K19">
-        <v>0.06749504388556039</v>
+        <v>-0.002203864569087263</v>
       </c>
       <c r="L19">
-        <v>0.06749504388556039</v>
+        <v>0.009534314393316173</v>
       </c>
       <c r="M19">
-        <v>0.06749504388556039</v>
+        <v>0.009624425288180638</v>
       </c>
       <c r="N19">
-        <v>0.06749504388556039</v>
+        <v>0.02823398990981295</v>
       </c>
       <c r="O19">
-        <v>0.06749504388556039</v>
+        <v>0.03161061037528465</v>
       </c>
       <c r="P19">
-        <v>0.06749504388556039</v>
+        <v>0.092474536536826</v>
       </c>
       <c r="Q19">
-        <v>0.06749504388556039</v>
+        <v>0.3133721527057863</v>
       </c>
       <c r="R19">
-        <v>0.06749504388556039</v>
+        <v>0.02107276553278428</v>
       </c>
       <c r="S19">
-        <v>0.06749504388556039</v>
+        <v>0.02334375582278558</v>
       </c>
       <c r="T19">
-        <v>0.06749504388556039</v>
+        <v>0.2754590313540272</v>
       </c>
       <c r="U19">
-        <v>0.06749504388556039</v>
+        <v>0.005400424907123363</v>
       </c>
       <c r="V19">
-        <v>0.06749504388556039</v>
+        <v>0.05839103968850205</v>
       </c>
       <c r="W19">
-        <v>0.06749504388556039</v>
+        <v>-0.0007525430988824383</v>
       </c>
       <c r="X19">
-        <v>0.06749504388556039</v>
+        <v>0.01098563584189462</v>
       </c>
       <c r="Y19">
-        <v>0.06749504388556039</v>
+        <v>0.0110757462122185</v>
       </c>
       <c r="Z19">
-        <v>0.06749504388556039</v>
+        <v>0.02968531151630432</v>
       </c>
       <c r="AA19">
-        <v>0.06749504388556039</v>
+        <v>0.03306193155781829</v>
       </c>
       <c r="AB19">
-        <v>0.06749504388556039</v>
+        <v>0.09392585689307054</v>
       </c>
       <c r="AC19">
-        <v>0.06749504388556039</v>
+        <v>0.3148234754543925</v>
       </c>
       <c r="AD19">
-        <v>0.06749504388556039</v>
+        <v>0.022524087153353</v>
       </c>
       <c r="AE19">
-        <v>0.06749504388556039</v>
+        <v>0.02479507641589949</v>
       </c>
       <c r="AF19">
-        <v>0.06749504388556039</v>
+        <v>0.2769103521266805</v>
       </c>
       <c r="AG19">
-        <v>0.06749504388556039</v>
+        <v>0.006851744350573286</v>
       </c>
       <c r="AH19">
-        <v>0.06749504388556039</v>
+        <v>0.05984235880857713</v>
       </c>
       <c r="AI19">
-        <v>0.06749504388556039</v>
+        <v>0.0006987744908237004</v>
       </c>
       <c r="AJ19">
-        <v>0.06749504388556039</v>
+        <v>0.01243695340997444</v>
       </c>
       <c r="AK19">
-        <v>0.06749504388556039</v>
+        <v>0.01252706375867203</v>
       </c>
       <c r="AL19">
-        <v>0.06749504388556039</v>
+        <v>0.03113662833705163</v>
       </c>
       <c r="AM19">
-        <v>0.06749504388556039</v>
+        <v>0.03451324946335053</v>
       </c>
       <c r="AN19">
-        <v>0.06749504388556039</v>
+        <v>0.09537717598397059</v>
       </c>
       <c r="AO19">
-        <v>0.06749504388556039</v>
+        <v>0.3162747910032667</v>
       </c>
       <c r="AP19">
-        <v>0.06749504388556039</v>
+        <v>0.02397541565578731</v>
       </c>
       <c r="AQ19">
-        <v>0.06749504388556039</v>
+        <v>0.02624640489670734</v>
       </c>
       <c r="AR19">
-        <v>0.06749504388556039</v>
+        <v>0.2783616800829476</v>
       </c>
       <c r="AS19">
-        <v>0.06749504388556039</v>
+        <v>0.008303066753157798</v>
       </c>
       <c r="AT19">
-        <v>0.06749504388556039</v>
+        <v>0.06129368118953524</v>
       </c>
       <c r="AU19">
-        <v>0.06749504388556039</v>
+        <v>0.002150098861812208</v>
       </c>
       <c r="AV19">
-        <v>0.06749504388556039</v>
+        <v>0.01388827775933653</v>
       </c>
       <c r="AW19">
-        <v>0.06749504388556039</v>
+        <v>0.01397838828757338</v>
       </c>
       <c r="AX19">
-        <v>0.06749504388556039</v>
+        <v>0.03258795284432656</v>
       </c>
       <c r="AY19">
-        <v>0.06749504388556039</v>
+        <v>0.03596457274200496</v>
       </c>
       <c r="AZ19">
-        <v>0.06749504388556039</v>
+        <v>0.09682849803400451</v>
       </c>
       <c r="BA19">
-        <v>0.06749504388556039</v>
+        <v>0.3177261132328401</v>
       </c>
       <c r="BB19">
-        <v>0.06749504388556039</v>
+        <v>0.02542672962303591</v>
       </c>
       <c r="BC19">
-        <v>0.06749504388556039</v>
+        <v>0.02769771922121749</v>
       </c>
       <c r="BD19">
-        <v>0.06749504388556039</v>
+        <v>0.2798129946979768</v>
       </c>
       <c r="BE19">
-        <v>0.06749504388556039</v>
+        <v>0.009754385516099348</v>
       </c>
       <c r="BF19">
-        <v>0.06749504388556039</v>
+        <v>0.06274500007620214</v>
       </c>
       <c r="BG19">
-        <v>0.06749504388556039</v>
+        <v>0.003601416650169345</v>
       </c>
       <c r="BH19">
-        <v>0.06749504388556039</v>
+        <v>0.01533959557973263</v>
       </c>
       <c r="BI19">
-        <v>0.06749504388556039</v>
+        <v>0.01542970611375527</v>
       </c>
       <c r="BJ19">
-        <v>0.06749504388556039</v>
+        <v>0.03403927087880267</v>
       </c>
       <c r="BK19">
-        <v>0.06749504388556039</v>
+        <v>0.03741589126207941</v>
       </c>
       <c r="BL19">
-        <v>0.06749504388556039</v>
+        <v>0.09827981708999287</v>
       </c>
       <c r="BM19">
-        <v>0.06749504388556039</v>
+        <v>0.3177261132328401</v>
       </c>
       <c r="BN19">
-        <v>0.06749504388556039</v>
+        <v>0.02542672962303591</v>
       </c>
       <c r="BO19">
-        <v>0.06749504388556039</v>
+        <v>0.02769771922121749</v>
       </c>
       <c r="BP19">
-        <v>0.06749504388556039</v>
+        <v>0.2798129946979768</v>
       </c>
       <c r="BQ19">
-        <v>0.06749504388556039</v>
+        <v>0.009754385516099348</v>
       </c>
       <c r="BR19">
-        <v>0.06749504388556039</v>
+        <v>0.06274500007620214</v>
       </c>
       <c r="BS19">
-        <v>0.06749504388556039</v>
+        <v>0.003601416650169345</v>
       </c>
       <c r="BT19">
-        <v>0.06749504388556039</v>
+        <v>0.01533959557973263</v>
       </c>
       <c r="BU19">
-        <v>0.06749504388556039</v>
+        <v>0.01542970611375527</v>
       </c>
       <c r="BV19">
-        <v>0.06749504388556039</v>
+        <v>0.03403927087880267</v>
       </c>
       <c r="BW19">
-        <v>0.06749504388556039</v>
+        <v>0.03741589126207941</v>
       </c>
       <c r="BX19">
-        <v>0.06749504388556039</v>
+        <v>0.09827981708999287</v>
       </c>
       <c r="BY19">
-        <v>82.63</v>
+        <v>135.43</v>
       </c>
     </row>
     <row r="20" spans="1:77">
@@ -4785,6 +4954,42 @@
       <c r="AN20">
         <v>0.0152</v>
       </c>
+      <c r="AO20">
+        <v>0.7752</v>
+      </c>
+      <c r="AP20">
+        <v>0.0152</v>
+      </c>
+      <c r="AQ20">
+        <v>0.0304</v>
+      </c>
+      <c r="AR20">
+        <v>0.0228</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0.038</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0.0228</v>
+      </c>
+      <c r="AW20">
+        <v>0.152</v>
+      </c>
+      <c r="AX20">
+        <v>0.076</v>
+      </c>
+      <c r="AY20">
+        <v>0.038</v>
+      </c>
+      <c r="AZ20">
+        <v>0.076</v>
+      </c>
       <c r="BA20">
         <v>0.1672</v>
       </c>
@@ -4822,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="BY20">
-        <v>176.45</v>
+        <v>205.1</v>
       </c>
     </row>
     <row r="21" spans="1:77">
@@ -4851,175 +5056,211 @@
         <v>97</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>0.07701350798499404</v>
       </c>
       <c r="K21">
-        <v>0.2508</v>
+        <v>0.2081134696861626</v>
       </c>
       <c r="L21">
-        <v>0.1499800664451827</v>
+        <v>0.08461383781357087</v>
       </c>
       <c r="M21">
-        <v>0.1005683168316832</v>
+        <v>0.1853142787282452</v>
       </c>
       <c r="N21">
-        <v>0.3553258171408404</v>
+        <v>0.409514034481311</v>
       </c>
       <c r="O21">
-        <v>0.3242288868819146</v>
+        <v>0.1701141291160853</v>
       </c>
       <c r="P21">
-        <v>0.2552592232342836</v>
+        <v>0.09601320231186485</v>
       </c>
       <c r="Q21">
-        <v>0.2144768860494199</v>
+        <v>0.3262085841018105</v>
       </c>
       <c r="R21">
-        <v>0.1843491615422013</v>
+        <v>0.0728770357202929</v>
       </c>
       <c r="S21">
-        <v>0.1615897521886792</v>
+        <v>0.07794063676055968</v>
       </c>
       <c r="T21">
-        <v>0.1503151757955994</v>
+        <v>0.08554086513813128</v>
       </c>
       <c r="U21">
-        <v>0.1202824787789404</v>
+        <v>0.04247888400203971</v>
       </c>
       <c r="V21">
-        <v>0.09965801937336694</v>
+        <v>0.03453763535169518</v>
       </c>
       <c r="W21">
-        <v>0.1039032079628221</v>
+        <v>0.1656375979123013</v>
       </c>
       <c r="X21">
-        <v>0.09565996219218879</v>
+        <v>0.04213796168970106</v>
       </c>
       <c r="Y21">
-        <v>0.1322519834710946</v>
+        <v>0.1428384041433059</v>
       </c>
       <c r="Z21">
-        <v>0.1674023140992253</v>
+        <v>0.367038164832767</v>
       </c>
       <c r="AA21">
-        <v>0.1645241961435871</v>
+        <v>0.1276382501345844</v>
       </c>
       <c r="AB21">
-        <v>0.1339350684233975</v>
+        <v>0.05353732271756671</v>
       </c>
       <c r="AC21">
-        <v>0.1091350621307125</v>
+        <v>0.2837327045742081</v>
       </c>
       <c r="AD21">
-        <v>0.08899452864494437</v>
+        <v>0.03040115569314213</v>
       </c>
       <c r="AE21">
-        <v>0.07261556045763314</v>
+        <v>0.03546475623386051</v>
       </c>
       <c r="AF21">
-        <v>0.05928074372059223</v>
+        <v>0.04306498411188372</v>
       </c>
       <c r="AG21">
-        <v>0.04841442760329593</v>
+        <v>3.002023248474539E-06</v>
       </c>
       <c r="AH21">
-        <v>0.03955308996696932</v>
+        <v>-0.007938245994156171</v>
       </c>
       <c r="AI21">
-        <v>0.03232242015655858</v>
+        <v>0.1231617169728921</v>
       </c>
       <c r="AJ21">
-        <v>0.02641943363391836</v>
+        <v>-0.000337920428749458</v>
       </c>
       <c r="AK21">
-        <v>0.02991951135613994</v>
+        <v>0.1003625217518046</v>
       </c>
       <c r="AL21">
-        <v>0.02446339971039475</v>
+        <v>0.3245622794502431</v>
       </c>
       <c r="AM21">
-        <v>0.02000467694007775</v>
+        <v>0.08516236062854973</v>
       </c>
       <c r="AN21">
-        <v>0.01912935947125506</v>
+        <v>0.01106143157949534</v>
+      </c>
+      <c r="AO21">
+        <v>0.2412568142955743</v>
+      </c>
+      <c r="AP21">
+        <v>-0.01207472240117146</v>
+      </c>
+      <c r="AQ21">
+        <v>-0.00701112100101553</v>
+      </c>
+      <c r="AR21">
+        <v>0.0005891079629428628</v>
+      </c>
+      <c r="AS21">
+        <v>-0.04247287315300602</v>
+      </c>
+      <c r="AT21">
+        <v>-0.05041412053747078</v>
+      </c>
+      <c r="AU21">
+        <v>0.08068584362876152</v>
+      </c>
+      <c r="AV21">
+        <v>-0.04281379313994016</v>
+      </c>
+      <c r="AW21">
+        <v>0.0578866500133003</v>
+      </c>
+      <c r="AX21">
+        <v>0.2820864099301623</v>
+      </c>
+      <c r="AY21">
+        <v>0.04268649287389702</v>
+      </c>
+      <c r="AZ21">
+        <v>-0.03141443497597334</v>
       </c>
       <c r="BA21">
-        <v>0.1568206728005674</v>
+        <v>0.1987809492790361</v>
       </c>
       <c r="BB21">
-        <v>0.1310371522737825</v>
+        <v>-0.05455059537408312</v>
       </c>
       <c r="BC21">
-        <v>0.1127195464985147</v>
+        <v>-0.04948699438035219</v>
       </c>
       <c r="BD21">
-        <v>0.09635596258397632</v>
+        <v>-0.04188676597386291</v>
       </c>
       <c r="BE21">
-        <v>0.07882391973897332</v>
+        <v>-0.08494874742077986</v>
       </c>
       <c r="BF21">
-        <v>0.0713969603987992</v>
+        <v>-0.09288999543813975</v>
       </c>
       <c r="BG21">
-        <v>0.05840935876796924</v>
+        <v>0.03820996741061949</v>
       </c>
       <c r="BH21">
-        <v>0.0519323445590943</v>
+        <v>-0.08528966815576941</v>
       </c>
       <c r="BI21">
-        <v>0.07013240755308923</v>
+        <v>0.01541077401974933</v>
       </c>
       <c r="BJ21">
-        <v>0.07119952768209878</v>
+        <v>0.239610532534213</v>
       </c>
       <c r="BK21">
-        <v>0.06516192997380943</v>
+        <v>0.0002106185488746724</v>
       </c>
       <c r="BL21">
-        <v>0.06713284070119903</v>
+        <v>-0.07389030923116148</v>
       </c>
       <c r="BM21">
-        <v>0.07015577470392</v>
+        <v>0.1987809492790361</v>
       </c>
       <c r="BN21">
-        <v>0.07015577470392</v>
+        <v>-0.05455059537408312</v>
       </c>
       <c r="BO21">
-        <v>0.07015577470392</v>
+        <v>-0.04948699438035219</v>
       </c>
       <c r="BP21">
-        <v>0.07015577470392</v>
+        <v>-0.04188676597386291</v>
       </c>
       <c r="BQ21">
-        <v>0.07015577470392</v>
+        <v>-0.08494874742077986</v>
       </c>
       <c r="BR21">
-        <v>0.07015577470392</v>
+        <v>-0.09288999543813975</v>
       </c>
       <c r="BS21">
-        <v>0.07015577470392</v>
+        <v>0.03820996741061949</v>
       </c>
       <c r="BT21">
-        <v>0.07015577470392</v>
+        <v>-0.08528966815576941</v>
       </c>
       <c r="BU21">
-        <v>0.07015577470392</v>
+        <v>0.01541077401974933</v>
       </c>
       <c r="BV21">
-        <v>0.07015577470392</v>
+        <v>0.239610532534213</v>
       </c>
       <c r="BW21">
-        <v>0.07015577470392</v>
+        <v>0.0002106185488746724</v>
       </c>
       <c r="BX21">
-        <v>0.07015577470392</v>
+        <v>-0.07389030923116148</v>
       </c>
       <c r="BY21">
-        <v>176.45</v>
+        <v>205.1</v>
       </c>
     </row>
     <row r="22" spans="1:77">
@@ -5248,205 +5489,205 @@
         <v>107</v>
       </c>
       <c r="J23">
-        <v>0.04190204004089342</v>
+        <v>0.0001989858774174361</v>
       </c>
       <c r="K23">
-        <v>0.04190204004089342</v>
+        <v>-0.004048834066084091</v>
       </c>
       <c r="L23">
-        <v>0.04190204004089342</v>
+        <v>-0.004060668191512941</v>
       </c>
       <c r="M23">
-        <v>0.04190204004089342</v>
+        <v>-0.01042892471849271</v>
       </c>
       <c r="N23">
-        <v>0.04190204004089342</v>
+        <v>0.004443385943145316</v>
       </c>
       <c r="O23">
-        <v>0.04190204004089342</v>
+        <v>0.1043548069640326</v>
       </c>
       <c r="P23">
-        <v>0.04190204004089342</v>
+        <v>-0.01040995779395407</v>
       </c>
       <c r="Q23">
-        <v>0.04190204004089342</v>
+        <v>0.3330608980963382</v>
       </c>
       <c r="R23">
-        <v>0.04190204004089342</v>
+        <v>0.04962192695005342</v>
       </c>
       <c r="S23">
-        <v>0.04190204004089342</v>
+        <v>-0.00702181617971518</v>
       </c>
       <c r="T23">
-        <v>0.04190204004089342</v>
+        <v>-0.007008224355441038</v>
       </c>
       <c r="U23">
-        <v>0.04190204004089342</v>
+        <v>-0.006995299258349179</v>
       </c>
       <c r="V23">
-        <v>0.04190204004089342</v>
+        <v>0.007189800052208518</v>
       </c>
       <c r="W23">
-        <v>0.04190204004089342</v>
+        <v>0.002941979117916611</v>
       </c>
       <c r="X23">
-        <v>0.04190204004089342</v>
+        <v>0.002930145268296123</v>
       </c>
       <c r="Y23">
-        <v>0.04190204004089342</v>
+        <v>-0.003438111742834524</v>
       </c>
       <c r="Z23">
-        <v>0.04190204004089342</v>
+        <v>0.01143419881463224</v>
       </c>
       <c r="AA23">
-        <v>0.04190204004089342</v>
+        <v>0.1113456190980489</v>
       </c>
       <c r="AB23">
-        <v>0.04190204004089342</v>
+        <v>-0.003419141964312832</v>
       </c>
       <c r="AC23">
-        <v>0.04190204004089342</v>
+        <v>0.3400517138218081</v>
       </c>
       <c r="AD23">
-        <v>0.04190204004089342</v>
+        <v>0.05661274257135215</v>
       </c>
       <c r="AE23">
-        <v>0.04190204004089342</v>
+        <v>-3.100319578518834E-05</v>
       </c>
       <c r="AF23">
-        <v>0.04190204004089342</v>
+        <v>-1.741147568231488E-05</v>
       </c>
       <c r="AG23">
-        <v>0.04190204004089342</v>
+        <v>-4.48648276172442E-06</v>
       </c>
       <c r="AH23">
-        <v>0.04190204004089342</v>
+        <v>0.0141806127236247</v>
       </c>
       <c r="AI23">
-        <v>0.04190204004089342</v>
+        <v>0.009932791811821412</v>
       </c>
       <c r="AJ23">
-        <v>0.04190204004089342</v>
+        <v>0.009920957478050038</v>
       </c>
       <c r="AK23">
-        <v>0.04190204004089342</v>
+        <v>0.003552700362748129</v>
       </c>
       <c r="AL23">
-        <v>0.04190204004089342</v>
+        <v>0.01842501081604363</v>
       </c>
       <c r="AM23">
-        <v>0.04190204004089342</v>
+        <v>0.1183364308686291</v>
       </c>
       <c r="AN23">
-        <v>0.04190204004089342</v>
+        <v>0.003571664382381483</v>
       </c>
       <c r="AO23">
-        <v>0.04190204004089342</v>
+        <v>0.3470425200643311</v>
       </c>
       <c r="AP23">
-        <v>0.04190204004089342</v>
+        <v>0.06360356390888876</v>
       </c>
       <c r="AQ23">
-        <v>0.04190204004089342</v>
+        <v>0.006959818037580168</v>
       </c>
       <c r="AR23">
-        <v>0.04190204004089342</v>
+        <v>0.006973409653511786</v>
       </c>
       <c r="AS23">
-        <v>0.04190204004089342</v>
+        <v>0.006986334542261122</v>
       </c>
       <c r="AT23">
-        <v>0.04190204004089342</v>
+        <v>0.0211714336444763</v>
       </c>
       <c r="AU23">
-        <v>0.04190204004089342</v>
+        <v>0.01692361262850174</v>
       </c>
       <c r="AV23">
-        <v>0.04190204004089342</v>
+        <v>0.0169117781905591</v>
       </c>
       <c r="AW23">
-        <v>0.04190204004089342</v>
+        <v>0.01054352097108593</v>
       </c>
       <c r="AX23">
-        <v>0.04190204004089342</v>
+        <v>0.02541583132021017</v>
       </c>
       <c r="AY23">
-        <v>0.04190204004089342</v>
+        <v>0.1253272512686244</v>
       </c>
       <c r="AZ23">
-        <v>0.04190204004089342</v>
+        <v>0.0105624846782055</v>
       </c>
       <c r="BA23">
-        <v>0.04190204004089342</v>
+        <v>0.3540333402559839</v>
       </c>
       <c r="BB23">
-        <v>0.04190204004089342</v>
+        <v>0.07059437407269345</v>
       </c>
       <c r="BC23">
-        <v>0.04190204004089342</v>
+        <v>0.01395062914915177</v>
       </c>
       <c r="BD23">
-        <v>0.04190204004089342</v>
+        <v>0.01396422086879272</v>
       </c>
       <c r="BE23">
-        <v>0.04190204004089342</v>
+        <v>0.0139771458614539</v>
       </c>
       <c r="BF23">
-        <v>0.04190204004089342</v>
+        <v>0.02816224506777353</v>
       </c>
       <c r="BG23">
-        <v>0.04190204004089342</v>
+        <v>0.02391442436727789</v>
       </c>
       <c r="BH23">
-        <v>0.04190204004089342</v>
+        <v>0.02390259018151668</v>
       </c>
       <c r="BI23">
-        <v>0.04190204004089342</v>
+        <v>0.01753433321404862</v>
       </c>
       <c r="BJ23">
-        <v>0.04190204004089342</v>
+        <v>0.03240664372028351</v>
       </c>
       <c r="BK23">
-        <v>0.04190204004089342</v>
+        <v>0.1323180640474231</v>
       </c>
       <c r="BL23">
-        <v>0.04190204004089342</v>
+        <v>0.01755329932452582</v>
       </c>
       <c r="BM23">
-        <v>0.04190204004089342</v>
+        <v>0.3540333402559839</v>
       </c>
       <c r="BN23">
-        <v>0.04190204004089342</v>
+        <v>0.07059437407269345</v>
       </c>
       <c r="BO23">
-        <v>0.04190204004089342</v>
+        <v>0.01395062914915177</v>
       </c>
       <c r="BP23">
-        <v>0.04190204004089342</v>
+        <v>0.01396422086879272</v>
       </c>
       <c r="BQ23">
-        <v>0.04190204004089342</v>
+        <v>0.0139771458614539</v>
       </c>
       <c r="BR23">
-        <v>0.04190204004089342</v>
+        <v>0.02816224506777353</v>
       </c>
       <c r="BS23">
-        <v>0.04190204004089342</v>
+        <v>0.02391442436727789</v>
       </c>
       <c r="BT23">
-        <v>0.04190204004089342</v>
+        <v>0.02390259018151668</v>
       </c>
       <c r="BU23">
-        <v>0.04190204004089342</v>
+        <v>0.01753433321404862</v>
       </c>
       <c r="BV23">
-        <v>0.04190204004089342</v>
+        <v>0.03240664372028351</v>
       </c>
       <c r="BW23">
-        <v>0.04190204004089342</v>
+        <v>0.1323180640474231</v>
       </c>
       <c r="BX23">
-        <v>0.04190204004089342</v>
+        <v>0.01755329932452582</v>
       </c>
       <c r="BY23">
         <v>100</v>
@@ -5678,205 +5919,205 @@
         <v>107</v>
       </c>
       <c r="J25">
-        <v>0.0001204881612837071</v>
+        <v>-0.000247395507632553</v>
       </c>
       <c r="K25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001980528389504387</v>
       </c>
       <c r="L25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001517501170112111</v>
       </c>
       <c r="M25">
-        <v>0.0001204881612837071</v>
+        <v>0.002571071030358446</v>
       </c>
       <c r="N25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0003995933892496629</v>
       </c>
       <c r="O25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0003555845335930765</v>
       </c>
       <c r="P25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0003120824885572584</v>
       </c>
       <c r="Q25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0002711835575519933</v>
       </c>
       <c r="R25">
-        <v>0.0001204881612837071</v>
+        <v>-0.000229958943105705</v>
       </c>
       <c r="S25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001904654632776646</v>
       </c>
       <c r="T25">
-        <v>0.0001204881612837071</v>
+        <v>-0.000152999067255742</v>
       </c>
       <c r="U25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001177981245442155</v>
       </c>
       <c r="V25">
-        <v>0.0001204881612837071</v>
+        <v>-8.379151430272213E-05</v>
       </c>
       <c r="W25">
-        <v>0.0001204881612837071</v>
+        <v>-5.395556006820081E-05</v>
       </c>
       <c r="X25">
-        <v>0.0001204881612837071</v>
+        <v>-2.677031833098E-05</v>
       </c>
       <c r="Y25">
-        <v>0.0001204881612837071</v>
+        <v>0.002677247246967737</v>
       </c>
       <c r="Z25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003555320741267794</v>
       </c>
       <c r="AA25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003670073461615859</v>
       </c>
       <c r="AB25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003726748922911749</v>
       </c>
       <c r="AC25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003714941580856408</v>
       </c>
       <c r="AD25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003673842959750858</v>
       </c>
       <c r="AE25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003592094954320441</v>
       </c>
       <c r="AF25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003475211329058242</v>
       </c>
       <c r="AG25">
-        <v>0.0001204881612837071</v>
+        <v>0.0003328523835745079</v>
       </c>
       <c r="AH25">
-        <v>0.0001204881612837071</v>
+        <v>0.000316968905473862</v>
       </c>
       <c r="AI25">
-        <v>0.0001204881612837071</v>
+        <v>0.0002975124253845425</v>
       </c>
       <c r="AJ25">
-        <v>0.0001204881612837071</v>
+        <v>0.0002765444665983465</v>
       </c>
       <c r="AK25">
-        <v>0.0001204881612837071</v>
+        <v>0.002934287637211937</v>
       </c>
       <c r="AL25">
-        <v>0.0001204881612837071</v>
+        <v>-9.871548676857109E-05</v>
       </c>
       <c r="AM25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001138279622343533</v>
       </c>
       <c r="AN25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001258624436383059</v>
       </c>
       <c r="AO25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001366279435338209</v>
       </c>
       <c r="AP25">
-        <v>0.0001204881612837071</v>
+        <v>-0.000142989051388281</v>
       </c>
       <c r="AQ25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001468682354359634</v>
       </c>
       <c r="AR25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001484943381993225</v>
       </c>
       <c r="AS25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001480988839040283</v>
       </c>
       <c r="AT25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001446578092052408</v>
       </c>
       <c r="AU25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0001412407589852431</v>
       </c>
       <c r="AV25">
-        <v>0.0001204881612837071</v>
+        <v>-0.000136462793770714</v>
       </c>
       <c r="AW25">
-        <v>0.0001204881612837071</v>
+        <v>0.00254899401018661</v>
       </c>
       <c r="AX25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004540512896623239</v>
       </c>
       <c r="AY25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004384514559907997</v>
       </c>
       <c r="AZ25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004191803604262661</v>
       </c>
       <c r="BA25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0003984989423833747</v>
       </c>
       <c r="BB25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004228538377032481</v>
       </c>
       <c r="BC25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004471976312984172</v>
       </c>
       <c r="BD25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004715313289298594</v>
       </c>
       <c r="BE25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004958562397037319</v>
       </c>
       <c r="BF25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0005189189867668201</v>
       </c>
       <c r="BG25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0005434081745338753</v>
       </c>
       <c r="BH25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0005678995147731354</v>
       </c>
       <c r="BI25">
-        <v>0.0001204881612837071</v>
+        <v>0.002086867091136716</v>
       </c>
       <c r="BJ25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0006165754230784032</v>
       </c>
       <c r="BK25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0006408287914394885</v>
       </c>
       <c r="BL25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0006651296027339354</v>
       </c>
       <c r="BM25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0003984989423833747</v>
       </c>
       <c r="BN25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004228538377032481</v>
       </c>
       <c r="BO25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004471976312984172</v>
       </c>
       <c r="BP25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004715313289298594</v>
       </c>
       <c r="BQ25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0004958562397037319</v>
       </c>
       <c r="BR25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0005189189867668201</v>
       </c>
       <c r="BS25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0005434081745338753</v>
       </c>
       <c r="BT25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0005678995147731354</v>
       </c>
       <c r="BU25">
-        <v>0.0001204881612837071</v>
+        <v>0.002086867091136716</v>
       </c>
       <c r="BV25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0006165754230784032</v>
       </c>
       <c r="BW25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0006408287914394885</v>
       </c>
       <c r="BX25">
-        <v>0.0001204881612837071</v>
+        <v>-0.0006651296027339354</v>
       </c>
       <c r="BY25">
         <v>100</v>
@@ -6003,6 +6244,42 @@
       <c r="AN26">
         <v>0.216</v>
       </c>
+      <c r="AO26">
+        <v>0.27</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0.54</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
       <c r="BA26">
         <v>0</v>
       </c>
@@ -6040,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="BY26">
-        <v>114.24</v>
+        <v>121.47</v>
       </c>
     </row>
     <row r="27" spans="1:77">
@@ -6069,175 +6346,211 @@
         <v>100</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J27">
-        <v>0.054</v>
+        <v>-0.01348796956768639</v>
       </c>
       <c r="K27">
-        <v>0.0243</v>
+        <v>-0.02689952212724028</v>
       </c>
       <c r="L27">
-        <v>0.01453156146179402</v>
+        <v>-0.02690356221154946</v>
       </c>
       <c r="M27">
-        <v>0.009744059405940593</v>
+        <v>-0.02697904187904718</v>
       </c>
       <c r="N27">
-        <v>0.006946804964608535</v>
+        <v>0.108073866622632</v>
       </c>
       <c r="O27">
-        <v>0.005142479760023222</v>
+        <v>0.0945489056939007</v>
       </c>
       <c r="P27">
-        <v>0.003903348716237711</v>
+        <v>0.02813381318599761</v>
       </c>
       <c r="Q27">
-        <v>0.003015318071992087</v>
+        <v>0.1800022839775823</v>
       </c>
       <c r="R27">
-        <v>0.002359290378372558</v>
+        <v>0.612064582435276</v>
       </c>
       <c r="S27">
-        <v>0.001863706889391955</v>
+        <v>-0.01777605253136093</v>
       </c>
       <c r="T27">
-        <v>0.001482974871844158</v>
+        <v>-0.01794232746754917</v>
       </c>
       <c r="U27">
-        <v>0.109077690896917</v>
+        <v>0.1619552808150895</v>
       </c>
       <c r="V27">
-        <v>0.08766909420127056</v>
+        <v>0.004463494810690291</v>
       </c>
       <c r="W27">
-        <v>0.07070746048715812</v>
+        <v>-0.008948058821024368</v>
       </c>
       <c r="X27">
-        <v>0.05718505688518677</v>
+        <v>-0.008952099172831296</v>
       </c>
       <c r="Y27">
-        <v>0.04635086195528619</v>
+        <v>-0.009027579107826783</v>
       </c>
       <c r="Z27">
-        <v>0.0376358825033633</v>
+        <v>0.1260253291263537</v>
       </c>
       <c r="AA27">
-        <v>0.03060313998744048</v>
+        <v>0.1125003679301248</v>
       </c>
       <c r="AB27">
-        <v>0.02571645252864399</v>
+        <v>0.04608527515472435</v>
       </c>
       <c r="AC27">
-        <v>0.08094794597820987</v>
+        <v>0.1979537457431833</v>
       </c>
       <c r="AD27">
-        <v>0.4148028296441434</v>
+        <v>0.6300160487613526</v>
       </c>
       <c r="AE27">
-        <v>0.3384605819330077</v>
+        <v>0.0001754416904171663</v>
       </c>
       <c r="AF27">
-        <v>0.2763071012692852</v>
+        <v>9.166486731118639E-06</v>
       </c>
       <c r="AG27">
-        <v>0.2256592834551693</v>
+        <v>0.1799067745018743</v>
       </c>
       <c r="AH27">
-        <v>0.1843566552829908</v>
+        <v>0.02241498018334773</v>
       </c>
       <c r="AI27">
-        <v>0.1506545576007054</v>
+        <v>0.009003426284135363</v>
       </c>
       <c r="AJ27">
-        <v>0.1231407817515032</v>
+        <v>0.008999385664830661</v>
       </c>
       <c r="AK27">
-        <v>0.1006700007182821</v>
+        <v>0.008923905462337414</v>
       </c>
       <c r="AL27">
-        <v>0.08231185453206516</v>
+        <v>0.1439768134290193</v>
       </c>
       <c r="AM27">
-        <v>0.1558884443606699</v>
+        <v>0.1304518519652927</v>
       </c>
       <c r="AN27">
-        <v>0.1668395853812691</v>
+        <v>0.06403676616435935</v>
+      </c>
+      <c r="AO27">
+        <v>0.2159052396395995</v>
+      </c>
+      <c r="AP27">
+        <v>0.6479675415856154</v>
+      </c>
+      <c r="AQ27">
+        <v>0.01812690608397917</v>
+      </c>
+      <c r="AR27">
+        <v>0.01796063061279535</v>
+      </c>
+      <c r="AS27">
+        <v>0.1978582383604396</v>
+      </c>
+      <c r="AT27">
+        <v>0.0403664437744163</v>
+      </c>
+      <c r="AU27">
+        <v>0.02695488960770624</v>
+      </c>
+      <c r="AV27">
+        <v>0.02695084872090377</v>
+      </c>
+      <c r="AW27">
+        <v>0.02687536825091276</v>
+      </c>
+      <c r="AX27">
+        <v>0.161928275950096</v>
+      </c>
+      <c r="AY27">
+        <v>0.1484033222655019</v>
+      </c>
+      <c r="AZ27">
+        <v>0.08198822895510513</v>
       </c>
       <c r="BA27">
-        <v>0.1856265772455689</v>
+        <v>0.233856698944196</v>
       </c>
       <c r="BB27">
-        <v>0.1518313228516865</v>
+        <v>0.6659190000841326</v>
       </c>
       <c r="BC27">
-        <v>0.1241955416963492</v>
+        <v>0.03607837423796909</v>
       </c>
       <c r="BD27">
-        <v>0.101594402706026</v>
+        <v>0.03591209903689715</v>
       </c>
       <c r="BE27">
-        <v>0.08310922157878423</v>
+        <v>0.2158097070521744</v>
       </c>
       <c r="BF27">
-        <v>0.06798943853477918</v>
+        <v>0.05831791541446969</v>
       </c>
       <c r="BG27">
-        <v>0.0556216887333694</v>
+        <v>0.04490636184926662</v>
       </c>
       <c r="BH27">
-        <v>0.04550461612346579</v>
+        <v>0.04490232136412332</v>
       </c>
       <c r="BI27">
-        <v>0.03722834667040845</v>
+        <v>0.04482684129573129</v>
       </c>
       <c r="BJ27">
-        <v>0.1286658069946833</v>
+        <v>0.1798797493953913</v>
       </c>
       <c r="BK27">
-        <v>0.1052669084053769</v>
+        <v>0.1663547900770861</v>
       </c>
       <c r="BL27">
-        <v>0.08612404639083618</v>
+        <v>0.09993969897807209</v>
       </c>
       <c r="BM27">
-        <v>0.09380403450429912</v>
+        <v>0.233856698944196</v>
       </c>
       <c r="BN27">
-        <v>0.09380403450429912</v>
+        <v>0.6659190000841326</v>
       </c>
       <c r="BO27">
-        <v>0.09380403450429912</v>
+        <v>0.03607837423796909</v>
       </c>
       <c r="BP27">
-        <v>0.09380403450429912</v>
+        <v>0.03591209903689715</v>
       </c>
       <c r="BQ27">
-        <v>0.09380403450429912</v>
+        <v>0.2158097070521744</v>
       </c>
       <c r="BR27">
-        <v>0.09380403450429912</v>
+        <v>0.05831791541446969</v>
       </c>
       <c r="BS27">
-        <v>0.09380403450429912</v>
+        <v>0.04490636184926662</v>
       </c>
       <c r="BT27">
-        <v>0.09380403450429912</v>
+        <v>0.04490232136412332</v>
       </c>
       <c r="BU27">
-        <v>0.09380403450429912</v>
+        <v>0.04482684129573129</v>
       </c>
       <c r="BV27">
-        <v>0.09380403450429912</v>
+        <v>0.1798797493953913</v>
       </c>
       <c r="BW27">
-        <v>0.09380403450429912</v>
+        <v>0.1663547900770861</v>
       </c>
       <c r="BX27">
-        <v>0.09380403450429912</v>
+        <v>0.09993969897807209</v>
       </c>
       <c r="BY27">
-        <v>114.24</v>
+        <v>121.47</v>
       </c>
     </row>
     <row r="28" spans="1:77">
@@ -6466,205 +6779,205 @@
         <v>107</v>
       </c>
       <c r="J29">
-        <v>0.0005527982771946599</v>
+        <v>0.003855147202706115</v>
       </c>
       <c r="K29">
-        <v>0.0005527982771946599</v>
+        <v>0.001793887818243964</v>
       </c>
       <c r="L29">
-        <v>0.0005527982771946599</v>
+        <v>0.001629918387271093</v>
       </c>
       <c r="M29">
-        <v>0.0005527982771946599</v>
+        <v>0.004444908129737589</v>
       </c>
       <c r="N29">
-        <v>0.0005527982771946599</v>
+        <v>0.0009430015888964315</v>
       </c>
       <c r="O29">
-        <v>0.0005527982771946599</v>
+        <v>0.0007976202697330682</v>
       </c>
       <c r="P29">
-        <v>0.0005527982771946599</v>
+        <v>0.0006600575611295789</v>
       </c>
       <c r="Q29">
-        <v>0.0005527982771946599</v>
+        <v>0.000300317430904204</v>
       </c>
       <c r="R29">
-        <v>0.0005527982771946599</v>
+        <v>0.0002016427113045815</v>
       </c>
       <c r="S29">
-        <v>0.0005527982771946599</v>
+        <v>0.0001104580061877826</v>
       </c>
       <c r="T29">
-        <v>0.0005527982771946599</v>
+        <v>2.673096726912437E-05</v>
       </c>
       <c r="U29">
-        <v>0.0005527982771946599</v>
+        <v>-4.964220242776392E-05</v>
       </c>
       <c r="V29">
-        <v>0.0005527982771946599</v>
+        <v>0.002642284046318116</v>
       </c>
       <c r="W29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0007652112486850359</v>
       </c>
       <c r="X29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0007649403612838394</v>
       </c>
       <c r="Y29">
-        <v>0.0005527982771946599</v>
+        <v>0.002222020093816412</v>
       </c>
       <c r="Z29">
-        <v>0.0005527982771946599</v>
+        <v>0.0003614442208029524</v>
       </c>
       <c r="AA29">
-        <v>0.0005527982771946599</v>
+        <v>0.000349171269490583</v>
       </c>
       <c r="AB29">
-        <v>0.0005527982771946599</v>
+        <v>0.0003348522657902967</v>
       </c>
       <c r="AC29">
-        <v>0.0005527982771946599</v>
+        <v>8.825710469237137E-05</v>
       </c>
       <c r="AD29">
-        <v>0.0005527982771946599</v>
+        <v>9.246658456820892E-05</v>
       </c>
       <c r="AE29">
-        <v>0.0005527982771946599</v>
+        <v>9.394034810648302E-05</v>
       </c>
       <c r="AF29">
-        <v>0.0005527982771946599</v>
+        <v>9.276625304739438E-05</v>
       </c>
       <c r="AG29">
-        <v>0.0005527982771946599</v>
+        <v>8.905806136826966E-05</v>
       </c>
       <c r="AH29">
-        <v>0.0005527982771946599</v>
+        <v>0.00284381311404832</v>
       </c>
       <c r="AI29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0005094831689526329</v>
       </c>
       <c r="AJ29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0004641393246502764</v>
       </c>
       <c r="AK29">
-        <v>0.0005527982771946599</v>
+        <v>0.002560411714941839</v>
       </c>
       <c r="AL29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0007357165164338579</v>
       </c>
       <c r="AM29">
-        <v>0.0005527982771946599</v>
+        <v>-0.000679159625025059</v>
       </c>
       <c r="AN29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0006210254654662304</v>
       </c>
       <c r="AO29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0007927191293182272</v>
       </c>
       <c r="AP29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0007122957574774067</v>
       </c>
       <c r="AQ29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0006342532468717711</v>
       </c>
       <c r="AR29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0005593818301200691</v>
       </c>
       <c r="AS29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0004883426322050759</v>
       </c>
       <c r="AT29">
-        <v>0.0005527982771946599</v>
+        <v>0.002338937129231227</v>
       </c>
       <c r="AU29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0009438022103923391</v>
       </c>
       <c r="AV29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008312841160797343</v>
       </c>
       <c r="AW29">
-        <v>0.0005527982771946599</v>
+        <v>0.00225673616136553</v>
       </c>
       <c r="AX29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0009790699627903457</v>
       </c>
       <c r="AY29">
-        <v>0.0005527982771946599</v>
+        <v>-0.000866525084745863</v>
       </c>
       <c r="AZ29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0007565658660796796</v>
       </c>
       <c r="BA29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008806819988459017</v>
       </c>
       <c r="BB29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008644305837215884</v>
       </c>
       <c r="BC29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008494343116038125</v>
       </c>
       <c r="BD29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008358928031335225</v>
       </c>
       <c r="BE29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008239990390369048</v>
       </c>
       <c r="BF29">
-        <v>0.0005527982771946599</v>
+        <v>0.001946422646386179</v>
       </c>
       <c r="BG29">
-        <v>0.0005527982771946599</v>
+        <v>-0.001053153356724938</v>
       </c>
       <c r="BH29">
-        <v>0.0005527982771946599</v>
+        <v>-0.001032525463009394</v>
       </c>
       <c r="BI29">
-        <v>0.0005527982771946599</v>
+        <v>0.001966720201082306</v>
       </c>
       <c r="BJ29">
-        <v>0.0005527982771946599</v>
+        <v>-0.000989776029203209</v>
       </c>
       <c r="BK29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0009681469178063149</v>
       </c>
       <c r="BL29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0009461698280596733</v>
       </c>
       <c r="BM29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008806819988459017</v>
       </c>
       <c r="BN29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008644305837215884</v>
       </c>
       <c r="BO29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008494343116038125</v>
       </c>
       <c r="BP29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008358928031335225</v>
       </c>
       <c r="BQ29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0008239990390369048</v>
       </c>
       <c r="BR29">
-        <v>0.0005527982771946599</v>
+        <v>0.001946422646386179</v>
       </c>
       <c r="BS29">
-        <v>0.0005527982771946599</v>
+        <v>-0.001053153356724938</v>
       </c>
       <c r="BT29">
-        <v>0.0005527982771946599</v>
+        <v>-0.001032525463009394</v>
       </c>
       <c r="BU29">
-        <v>0.0005527982771946599</v>
+        <v>0.001966720201082306</v>
       </c>
       <c r="BV29">
-        <v>0.0005527982771946599</v>
+        <v>-0.000989776029203209</v>
       </c>
       <c r="BW29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0009681469178063149</v>
       </c>
       <c r="BX29">
-        <v>0.0005527982771946599</v>
+        <v>-0.0009461698280596733</v>
       </c>
       <c r="BY29">
         <v>100</v>
@@ -6791,6 +7104,42 @@
       <c r="AN30">
         <v>124.54284</v>
       </c>
+      <c r="AO30">
+        <v>140.59344</v>
+      </c>
+      <c r="AP30">
+        <v>91.60786</v>
+      </c>
+      <c r="AQ30">
+        <v>140.89062</v>
+      </c>
+      <c r="AR30">
+        <v>157.25108</v>
+      </c>
+      <c r="AS30">
+        <v>125.863</v>
+      </c>
+      <c r="AT30">
+        <v>124.237</v>
+      </c>
+      <c r="AU30">
+        <v>112.6363200000001</v>
+      </c>
+      <c r="AV30">
+        <v>153.7479599999999</v>
+      </c>
+      <c r="AW30">
+        <v>155.694</v>
+      </c>
+      <c r="AX30">
+        <v>171.386</v>
+      </c>
+      <c r="AY30">
+        <v>94.5026</v>
+      </c>
+      <c r="AZ30">
+        <v>199.7359999999999</v>
+      </c>
       <c r="BA30">
         <v>108.417</v>
       </c>
@@ -6828,7 +7177,7 @@
         <v>77.98999999999999</v>
       </c>
       <c r="BY30">
-        <v>54.42</v>
+        <v>80.03</v>
       </c>
     </row>
     <row r="31" spans="1:77">
@@ -6857,175 +7206,211 @@
         <v>102</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J31">
-        <v>91.05299999999998</v>
+        <v>75.80709931942792</v>
       </c>
       <c r="K31">
-        <v>88.65719999999997</v>
+        <v>74.11627470675157</v>
       </c>
       <c r="L31">
-        <v>90.48136544850496</v>
+        <v>71.73689464412482</v>
       </c>
       <c r="M31">
-        <v>99.24970173267324</v>
+        <v>70.36390523491298</v>
       </c>
       <c r="N31">
-        <v>95.50067770304501</v>
+        <v>139.935686011372</v>
       </c>
       <c r="O31">
-        <v>96.94254785633164</v>
+        <v>77.17833175210292</v>
       </c>
       <c r="P31">
-        <v>103.7024281877919</v>
+        <v>116.9218816085446</v>
       </c>
       <c r="Q31">
-        <v>103.9607762476994</v>
+        <v>113.0444167396898</v>
       </c>
       <c r="R31">
-        <v>111.6347778105814</v>
+        <v>114.5870337548165</v>
       </c>
       <c r="S31">
-        <v>113.8870802928562</v>
+        <v>107.7555914699669</v>
       </c>
       <c r="T31">
-        <v>109.3378417748324</v>
+        <v>99.68165862316101</v>
       </c>
       <c r="U31">
-        <v>105.0800545106576</v>
+        <v>118.9073691427694</v>
       </c>
       <c r="V31">
-        <v>98.70364838465939</v>
+        <v>93.30625208953936</v>
       </c>
       <c r="W31">
-        <v>91.7976536922845</v>
+        <v>91.6154171123856</v>
       </c>
       <c r="X31">
-        <v>75.4328704940046</v>
+        <v>89.23602822894327</v>
       </c>
       <c r="Y31">
-        <v>72.92351723688637</v>
+        <v>87.86301715188863</v>
       </c>
       <c r="Z31">
-        <v>80.9472303808538</v>
+        <v>157.4347527411884</v>
       </c>
       <c r="AA31">
-        <v>85.73700147594667</v>
+        <v>94.67742153412387</v>
       </c>
       <c r="AB31">
-        <v>92.46326206767412</v>
+        <v>134.4209641275594</v>
       </c>
       <c r="AC31">
-        <v>102.5554731339016</v>
+        <v>130.543489554028</v>
       </c>
       <c r="AD31">
-        <v>114.5440336269262</v>
+        <v>132.0861216010354</v>
       </c>
       <c r="AE31">
-        <v>114.1943425750818</v>
+        <v>125.2546796522835</v>
       </c>
       <c r="AF31">
-        <v>111.8812030945471</v>
+        <v>117.1807336830434</v>
       </c>
       <c r="AG31">
-        <v>127.1532076261742</v>
+        <v>136.4064363441869</v>
       </c>
       <c r="AH31">
-        <v>125.9824159507237</v>
+        <v>110.8053460358442</v>
       </c>
       <c r="AI31">
-        <v>128.3977799492233</v>
+        <v>109.114517298119</v>
       </c>
       <c r="AJ31">
-        <v>130.2217283130161</v>
+        <v>106.7351303080252</v>
       </c>
       <c r="AK31">
-        <v>115.7072856325199</v>
+        <v>105.3621647641108</v>
       </c>
       <c r="AL31">
-        <v>147.6789287301752</v>
+        <v>174.9338884108998</v>
       </c>
       <c r="AM31">
-        <v>140.8997452302186</v>
+        <v>112.176613470488</v>
       </c>
       <c r="AN31">
-        <v>137.9198393879632</v>
+        <v>151.9201461623117</v>
+      </c>
+      <c r="AO31">
+        <v>148.0426749814412</v>
+      </c>
+      <c r="AP31">
+        <v>149.585305459967</v>
+      </c>
+      <c r="AQ31">
+        <v>142.753826075474</v>
+      </c>
+      <c r="AR31">
+        <v>134.6798822403332</v>
+      </c>
+      <c r="AS31">
+        <v>153.905614190919</v>
+      </c>
+      <c r="AT31">
+        <v>128.3044880136722</v>
+      </c>
+      <c r="AU31">
+        <v>126.6136606477295</v>
+      </c>
+      <c r="AV31">
+        <v>124.2342621954249</v>
+      </c>
+      <c r="AW31">
+        <v>122.8612740035466</v>
+      </c>
+      <c r="AX31">
+        <v>192.4330648787313</v>
+      </c>
+      <c r="AY31">
+        <v>129.6757228939005</v>
+      </c>
+      <c r="AZ31">
+        <v>169.4192400033424</v>
       </c>
       <c r="BA31">
-        <v>138.4067404258502</v>
+        <v>165.5417894530307</v>
       </c>
       <c r="BB31">
-        <v>129.8865161518866</v>
+        <v>167.0844090184353</v>
       </c>
       <c r="BC31">
-        <v>131.8894428210702</v>
+        <v>160.252959592841</v>
       </c>
       <c r="BD31">
-        <v>136.504760561739</v>
+        <v>152.1790225067662</v>
       </c>
       <c r="BE31">
-        <v>134.5684838943551</v>
+        <v>171.4047354386937</v>
       </c>
       <c r="BF31">
-        <v>132.6889115432027</v>
+        <v>145.8036229424572</v>
       </c>
       <c r="BG31">
-        <v>129.0412062463082</v>
+        <v>144.1127941380354</v>
       </c>
       <c r="BH31">
-        <v>133.5351370738911</v>
+        <v>141.7334105691656</v>
       </c>
       <c r="BI31">
-        <v>137.5653374353719</v>
+        <v>140.3604152786907</v>
       </c>
       <c r="BJ31">
-        <v>143.7161923431895</v>
+        <v>209.9321835370372</v>
       </c>
       <c r="BK31">
-        <v>134.7663098269952</v>
+        <v>147.1748436078514</v>
       </c>
       <c r="BL31">
-        <v>146.5810941020292</v>
+        <v>186.918379181437</v>
       </c>
       <c r="BM31">
-        <v>136.9797383106437</v>
+        <v>165.5417894530307</v>
       </c>
       <c r="BN31">
-        <v>136.9797383106437</v>
+        <v>167.0844090184353</v>
       </c>
       <c r="BO31">
-        <v>136.9797383106437</v>
+        <v>160.252959592841</v>
       </c>
       <c r="BP31">
-        <v>136.9797383106437</v>
+        <v>152.1790225067662</v>
       </c>
       <c r="BQ31">
-        <v>136.9797383106437</v>
+        <v>171.4047354386937</v>
       </c>
       <c r="BR31">
-        <v>136.9797383106437</v>
+        <v>145.8036229424572</v>
       </c>
       <c r="BS31">
-        <v>136.9797383106437</v>
+        <v>144.1127941380354</v>
       </c>
       <c r="BT31">
-        <v>136.9797383106437</v>
+        <v>141.7334105691656</v>
       </c>
       <c r="BU31">
-        <v>136.9797383106437</v>
+        <v>140.3604152786907</v>
       </c>
       <c r="BV31">
-        <v>136.9797383106437</v>
+        <v>209.9321835370372</v>
       </c>
       <c r="BW31">
-        <v>136.9797383106437</v>
+        <v>147.1748436078514</v>
       </c>
       <c r="BX31">
-        <v>136.9797383106437</v>
+        <v>186.918379181437</v>
       </c>
       <c r="BY31">
-        <v>54.42</v>
+        <v>80.03</v>
       </c>
     </row>
     <row r="32" spans="1:77">
@@ -7149,6 +7534,42 @@
       <c r="AN32">
         <v>46.99644000000001</v>
       </c>
+      <c r="AO32">
+        <v>38.05708000000001</v>
+      </c>
+      <c r="AP32">
+        <v>50.67052</v>
+      </c>
+      <c r="AQ32">
+        <v>116.4836</v>
+      </c>
+      <c r="AR32">
+        <v>18.831</v>
+      </c>
+      <c r="AS32">
+        <v>117.26</v>
+      </c>
+      <c r="AT32">
+        <v>67.05799999999999</v>
+      </c>
+      <c r="AU32">
+        <v>101.01128</v>
+      </c>
+      <c r="AV32">
+        <v>73.774</v>
+      </c>
+      <c r="AW32">
+        <v>91.05</v>
+      </c>
+      <c r="AX32">
+        <v>125.512</v>
+      </c>
+      <c r="AY32">
+        <v>51.03209</v>
+      </c>
+      <c r="AZ32">
+        <v>108.676</v>
+      </c>
       <c r="BA32">
         <v>80.89099999999999</v>
       </c>
@@ -7186,7 +7607,7 @@
         <v>41.848608</v>
       </c>
       <c r="BY32">
-        <v>75.93000000000001</v>
+        <v>88.73999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:77">
@@ -7215,175 +7636,211 @@
         <v>103</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J33">
-        <v>78.22700000000002</v>
+        <v>78.00511767630005</v>
       </c>
       <c r="K33">
-        <v>85.57995</v>
+        <v>92.92342673754602</v>
       </c>
       <c r="L33">
-        <v>80.6471096345515</v>
+        <v>53.68984149177584</v>
       </c>
       <c r="M33">
-        <v>81.20220594059407</v>
+        <v>72.93792377912801</v>
       </c>
       <c r="N33">
-        <v>79.23893946257917</v>
+        <v>89.89298109221515</v>
       </c>
       <c r="O33">
-        <v>81.19345761342291</v>
+        <v>69.44541778468283</v>
       </c>
       <c r="P33">
-        <v>83.71691963644285</v>
+        <v>84.9029889677402</v>
       </c>
       <c r="Q33">
-        <v>83.34178247255886</v>
+        <v>59.16732139856732</v>
       </c>
       <c r="R33">
-        <v>86.82515867450483</v>
+        <v>87.11570542105385</v>
       </c>
       <c r="S33">
-        <v>85.18136863492114</v>
+        <v>86.06577202466548</v>
       </c>
       <c r="T33">
-        <v>93.29951997315158</v>
+        <v>65.69008628473118</v>
       </c>
       <c r="U33">
-        <v>91.08025781153347</v>
+        <v>94.90801169334519</v>
       </c>
       <c r="V33">
-        <v>87.89376100423686</v>
+        <v>77.24001904124412</v>
       </c>
       <c r="W33">
-        <v>79.46289627725665</v>
+        <v>92.15832776428219</v>
       </c>
       <c r="X33">
-        <v>65.68393533568994</v>
+        <v>52.92473998838395</v>
       </c>
       <c r="Y33">
-        <v>66.30764495910752</v>
+        <v>72.17281589289959</v>
       </c>
       <c r="Z33">
-        <v>69.44418107236547</v>
+        <v>89.12787032447039</v>
       </c>
       <c r="AA33">
-        <v>69.22305129337279</v>
+        <v>68.68031018992525</v>
       </c>
       <c r="AB33">
-        <v>72.99492041828672</v>
+        <v>84.1378790766837</v>
       </c>
       <c r="AC33">
-        <v>69.73952284289118</v>
+        <v>58.40221254556828</v>
       </c>
       <c r="AD33">
-        <v>76.97468950938196</v>
+        <v>86.35059355704968</v>
       </c>
       <c r="AE33">
-        <v>73.96908728351147</v>
+        <v>85.30065967298891</v>
       </c>
       <c r="AF33">
-        <v>69.60044161651433</v>
+        <v>64.92497716746696</v>
       </c>
       <c r="AG33">
-        <v>71.989527121172</v>
+        <v>94.14289099450721</v>
       </c>
       <c r="AH33">
-        <v>74.73621239166246</v>
+        <v>76.47489918813595</v>
       </c>
       <c r="AI33">
-        <v>84.75959471728525</v>
+        <v>91.39320576841095</v>
       </c>
       <c r="AJ33">
-        <v>79.11974360060509</v>
+        <v>52.15962561972198</v>
       </c>
       <c r="AK33">
-        <v>72.71034827039749</v>
+        <v>71.40770865852305</v>
       </c>
       <c r="AL33">
-        <v>72.59315150896886</v>
+        <v>88.36276077874268</v>
       </c>
       <c r="AM33">
-        <v>71.87443246858412</v>
+        <v>67.91520017394045</v>
       </c>
       <c r="AN33">
-        <v>67.34215242799549</v>
+        <v>83.37276957663944</v>
+      </c>
+      <c r="AO33">
+        <v>57.63709882440637</v>
+      </c>
+      <c r="AP33">
+        <v>85.5854802337131</v>
+      </c>
+      <c r="AQ33">
+        <v>84.53553796935428</v>
+      </c>
+      <c r="AR33">
+        <v>64.15986108475299</v>
+      </c>
+      <c r="AS33">
+        <v>93.37777249172392</v>
+      </c>
+      <c r="AT33">
+        <v>75.70978533655946</v>
+      </c>
+      <c r="AU33">
+        <v>90.6280922393278</v>
+      </c>
+      <c r="AV33">
+        <v>51.3945070630588</v>
+      </c>
+      <c r="AW33">
+        <v>70.64258980225593</v>
+      </c>
+      <c r="AX33">
+        <v>87.59764686796508</v>
+      </c>
+      <c r="AY33">
+        <v>67.15009218743529</v>
+      </c>
+      <c r="AZ33">
+        <v>82.60765746396918</v>
       </c>
       <c r="BA33">
-        <v>62.00892049515014</v>
+        <v>56.87199333348966</v>
       </c>
       <c r="BB33">
-        <v>59.94464643030867</v>
+        <v>84.82037533991598</v>
       </c>
       <c r="BC33">
-        <v>70.23565963006891</v>
+        <v>83.77044090444757</v>
       </c>
       <c r="BD33">
-        <v>60.88102546864318</v>
+        <v>63.39475570055998</v>
       </c>
       <c r="BE33">
-        <v>71.13922403294723</v>
+        <v>92.61267600820229</v>
       </c>
       <c r="BF33">
-        <v>70.3967405785252</v>
+        <v>74.94468444581938</v>
       </c>
       <c r="BG33">
-        <v>75.965737352289</v>
+        <v>89.86299346565542</v>
       </c>
       <c r="BH33">
-        <v>75.56708052543068</v>
+        <v>50.62940825018992</v>
       </c>
       <c r="BI33">
-        <v>78.38307644865407</v>
+        <v>69.87748890683413</v>
       </c>
       <c r="BJ33">
-        <v>86.95426189400173</v>
+        <v>86.83254545961402</v>
       </c>
       <c r="BK33">
-        <v>80.42152971838875</v>
+        <v>66.38498361129592</v>
       </c>
       <c r="BL33">
-        <v>85.55962519481294</v>
+        <v>81.84255144299975</v>
       </c>
       <c r="BM33">
-        <v>77.75670343062323</v>
+        <v>56.87199333348966</v>
       </c>
       <c r="BN33">
-        <v>77.75670343062323</v>
+        <v>84.82037533991598</v>
       </c>
       <c r="BO33">
-        <v>77.75670343062323</v>
+        <v>83.77044090444757</v>
       </c>
       <c r="BP33">
-        <v>77.75670343062323</v>
+        <v>63.39475570055998</v>
       </c>
       <c r="BQ33">
-        <v>77.75670343062323</v>
+        <v>92.61267600820229</v>
       </c>
       <c r="BR33">
-        <v>77.75670343062323</v>
+        <v>74.94468444581938</v>
       </c>
       <c r="BS33">
-        <v>77.75670343062323</v>
+        <v>89.86299346565542</v>
       </c>
       <c r="BT33">
-        <v>77.75670343062323</v>
+        <v>50.62940825018992</v>
       </c>
       <c r="BU33">
-        <v>77.75670343062323</v>
+        <v>69.87748890683413</v>
       </c>
       <c r="BV33">
-        <v>77.75670343062323</v>
+        <v>86.83254545961402</v>
       </c>
       <c r="BW33">
-        <v>77.75670343062323</v>
+        <v>66.38498361129592</v>
       </c>
       <c r="BX33">
-        <v>77.75670343062323</v>
+        <v>81.84255144299975</v>
       </c>
       <c r="BY33">
-        <v>75.93000000000001</v>
+        <v>88.73999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:77">
@@ -7507,6 +7964,42 @@
       <c r="AN34">
         <v>2.664908</v>
       </c>
+      <c r="AO34">
+        <v>17.854602</v>
+      </c>
+      <c r="AP34">
+        <v>7.766</v>
+      </c>
+      <c r="AQ34">
+        <v>26.98835</v>
+      </c>
+      <c r="AR34">
+        <v>2.8192</v>
+      </c>
+      <c r="AS34">
+        <v>5.718999999999999</v>
+      </c>
+      <c r="AT34">
+        <v>1.589</v>
+      </c>
+      <c r="AU34">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV34">
+        <v>3.222</v>
+      </c>
+      <c r="AW34">
+        <v>3.268</v>
+      </c>
+      <c r="AX34">
+        <v>2.162</v>
+      </c>
+      <c r="AY34">
+        <v>13.032</v>
+      </c>
+      <c r="AZ34">
+        <v>4.1454</v>
+      </c>
       <c r="BA34">
         <v>10.1374</v>
       </c>
@@ -7544,7 +8037,7 @@
         <v>1.853</v>
       </c>
       <c r="BY34">
-        <v>99.73999999999999</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="35" spans="1:77">
@@ -7573,175 +8066,211 @@
         <v>104</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J35">
-        <v>5.555166000000001</v>
+        <v>5.714145000616432</v>
       </c>
       <c r="K35">
-        <v>8.115874700000001</v>
+        <v>5.845455598139478</v>
       </c>
       <c r="L35">
-        <v>6.908739023255815</v>
+        <v>6.212344400955698</v>
       </c>
       <c r="M35">
-        <v>10.58357104306931</v>
+        <v>15.8958884341971</v>
       </c>
       <c r="N35">
-        <v>10.02160563765417</v>
+        <v>8.477454397249424</v>
       </c>
       <c r="O35">
-        <v>9.609509349311358</v>
+        <v>10.03340455287795</v>
       </c>
       <c r="P35">
-        <v>9.561917530268696</v>
+        <v>8.779424921403573</v>
       </c>
       <c r="Q35">
-        <v>11.27833275124304</v>
+        <v>12.95638146938955</v>
       </c>
       <c r="R35">
-        <v>18.45607799935507</v>
+        <v>26.7784229002061</v>
       </c>
       <c r="S35">
-        <v>16.8341591494896</v>
+        <v>24.43277194692942</v>
       </c>
       <c r="T35">
-        <v>14.73450365400799</v>
+        <v>5.958552609123493</v>
       </c>
       <c r="U35">
-        <v>12.37398744687849</v>
+        <v>10.56960198722928</v>
       </c>
       <c r="V35">
-        <v>10.19893407083436</v>
+        <v>4.6432396985084</v>
       </c>
       <c r="W35">
-        <v>9.153803767024868</v>
+        <v>4.774550248524069</v>
       </c>
       <c r="X35">
-        <v>7.403190349740038</v>
+        <v>5.141438986173694</v>
       </c>
       <c r="Y35">
-        <v>6.114268131086178</v>
+        <v>14.82498295914761</v>
       </c>
       <c r="Z35">
-        <v>5.457269023037186</v>
+        <v>7.406548677094976</v>
       </c>
       <c r="AA35">
-        <v>4.913635166524257</v>
+        <v>8.962498758878649</v>
       </c>
       <c r="AB35">
-        <v>6.318178912384131</v>
+        <v>7.708519055520384</v>
       </c>
       <c r="AC35">
-        <v>5.277151539590629</v>
+        <v>11.88547566535236</v>
       </c>
       <c r="AD35">
-        <v>8.932996952378337</v>
+        <v>25.70751686750034</v>
       </c>
       <c r="AE35">
-        <v>13.24559172771423</v>
+        <v>23.36186564207924</v>
       </c>
       <c r="AF35">
-        <v>11.78424156478515</v>
+        <v>4.8876466442476</v>
       </c>
       <c r="AG35">
-        <v>13.26381609902012</v>
+        <v>9.498696019022136</v>
       </c>
       <c r="AH35">
-        <v>12.29945979639697</v>
+        <v>3.572333999647254</v>
       </c>
       <c r="AI35">
-        <v>10.30474426334494</v>
+        <v>3.703644666013998</v>
       </c>
       <c r="AJ35">
-        <v>10.26516064122792</v>
+        <v>4.07053336847954</v>
       </c>
       <c r="AK35">
-        <v>14.82000673348463</v>
+        <v>13.7540775078293</v>
       </c>
       <c r="AL35">
-        <v>14.68451228495646</v>
+        <v>6.335643759768935</v>
       </c>
       <c r="AM35">
-        <v>13.77493671394425</v>
+        <v>7.891594028732487</v>
       </c>
       <c r="AN35">
-        <v>11.7509083903501</v>
+        <v>6.637614448704209</v>
+      </c>
+      <c r="AO35">
+        <v>10.81457092728548</v>
+      </c>
+      <c r="AP35">
+        <v>24.63661240239399</v>
+      </c>
+      <c r="AQ35">
+        <v>22.29096093452385</v>
+      </c>
+      <c r="AR35">
+        <v>3.816741871935221</v>
+      </c>
+      <c r="AS35">
+        <v>8.427791226275859</v>
+      </c>
+      <c r="AT35">
+        <v>2.501429011330256</v>
+      </c>
+      <c r="AU35">
+        <v>2.632739597644637</v>
+      </c>
+      <c r="AV35">
+        <v>2.999628304122704</v>
+      </c>
+      <c r="AW35">
+        <v>12.68317235756136</v>
+      </c>
+      <c r="AX35">
+        <v>5.26473814720425</v>
+      </c>
+      <c r="AY35">
+        <v>6.820688253809107</v>
+      </c>
+      <c r="AZ35">
+        <v>5.566708739416085</v>
       </c>
       <c r="BA35">
-        <v>12.86247858527883</v>
+        <v>9.743665256637678</v>
       </c>
       <c r="BB35">
-        <v>11.93461150472271</v>
+        <v>23.56570662542332</v>
       </c>
       <c r="BC35">
-        <v>14.67463783665121</v>
+        <v>21.22005541070632</v>
       </c>
       <c r="BD35">
-        <v>12.51718198374787</v>
+        <v>2.745836277644911</v>
       </c>
       <c r="BE35">
-        <v>11.28024744839597</v>
+        <v>7.356885646817389</v>
       </c>
       <c r="BF35">
-        <v>9.51715117505872</v>
+        <v>1.430523472442371</v>
       </c>
       <c r="BG35">
-        <v>7.887783334201176</v>
+        <v>1.561834072341655</v>
       </c>
       <c r="BH35">
-        <v>7.039120342315566</v>
+        <v>1.928722809906104</v>
       </c>
       <c r="BI35">
-        <v>6.353238101089171</v>
+        <v>11.61226685957938</v>
       </c>
       <c r="BJ35">
-        <v>5.59099113461849</v>
+        <v>4.193832790239997</v>
       </c>
       <c r="BK35">
-        <v>6.944197677289039</v>
+        <v>5.749782943648222</v>
       </c>
       <c r="BL35">
-        <v>6.435234333019069</v>
+        <v>4.495803336130181</v>
       </c>
       <c r="BM35">
-        <v>8.171627381898448</v>
+        <v>9.743665256637678</v>
       </c>
       <c r="BN35">
-        <v>8.171627381898448</v>
+        <v>23.56570662542332</v>
       </c>
       <c r="BO35">
-        <v>8.171627381898448</v>
+        <v>21.22005541070632</v>
       </c>
       <c r="BP35">
-        <v>8.171627381898448</v>
+        <v>2.745836277644911</v>
       </c>
       <c r="BQ35">
-        <v>8.171627381898448</v>
+        <v>7.356885646817389</v>
       </c>
       <c r="BR35">
-        <v>8.171627381898448</v>
+        <v>1.430523472442371</v>
       </c>
       <c r="BS35">
-        <v>8.171627381898448</v>
+        <v>1.561834072341655</v>
       </c>
       <c r="BT35">
-        <v>8.171627381898448</v>
+        <v>1.928722809906104</v>
       </c>
       <c r="BU35">
-        <v>8.171627381898448</v>
+        <v>11.61226685957938</v>
       </c>
       <c r="BV35">
-        <v>8.171627381898448</v>
+        <v>4.193832790239997</v>
       </c>
       <c r="BW35">
-        <v>8.171627381898448</v>
+        <v>5.749782943648222</v>
       </c>
       <c r="BX35">
-        <v>8.171627381898448</v>
+        <v>4.495803336130181</v>
       </c>
       <c r="BY35">
-        <v>99.73999999999999</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="36" spans="1:77">
@@ -7865,6 +8394,42 @@
       <c r="AN36">
         <v>39.11843</v>
       </c>
+      <c r="AO36">
+        <v>21.429709</v>
+      </c>
+      <c r="AP36">
+        <v>25.32719999999999</v>
+      </c>
+      <c r="AQ36">
+        <v>27.849708</v>
+      </c>
+      <c r="AR36">
+        <v>4.669</v>
+      </c>
+      <c r="AS36">
+        <v>22.27845000000001</v>
+      </c>
+      <c r="AT36">
+        <v>25.34200000000001</v>
+      </c>
+      <c r="AU36">
+        <v>28.91584</v>
+      </c>
+      <c r="AV36">
+        <v>27.71202</v>
+      </c>
+      <c r="AW36">
+        <v>24.02848</v>
+      </c>
+      <c r="AX36">
+        <v>44.31400000000001</v>
+      </c>
+      <c r="AY36">
+        <v>20.582</v>
+      </c>
+      <c r="AZ36">
+        <v>29.596</v>
+      </c>
       <c r="BA36">
         <v>38.026</v>
       </c>
@@ -7902,7 +8467,7 @@
         <v>14.937</v>
       </c>
       <c r="BY36">
-        <v>50.51</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="37" spans="1:77">
@@ -7931,175 +8496,211 @@
         <v>105</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J37">
-        <v>54.866372</v>
+        <v>38.55132831708768</v>
       </c>
       <c r="K37">
-        <v>37.8326674</v>
+        <v>29.56255757779605</v>
       </c>
       <c r="L37">
-        <v>32.04490077076412</v>
+        <v>28.56285420851458</v>
       </c>
       <c r="M37">
-        <v>33.68529212574257</v>
+        <v>30.97016036201249</v>
       </c>
       <c r="N37">
-        <v>30.07272459506676</v>
+        <v>53.85148071605895</v>
       </c>
       <c r="O37">
-        <v>32.10963440418185</v>
+        <v>29.22355783160549</v>
       </c>
       <c r="P37">
-        <v>34.65882785488352</v>
+        <v>43.12218426979654</v>
       </c>
       <c r="Q37">
-        <v>38.15893766130849</v>
+        <v>40.97569192691807</v>
       </c>
       <c r="R37">
-        <v>41.8696712112651</v>
+        <v>54.62426187065094</v>
       </c>
       <c r="S37">
-        <v>41.03527934651387</v>
+        <v>43.22091345916726</v>
       </c>
       <c r="T37">
-        <v>39.6667616162707</v>
+        <v>27.79492063446072</v>
       </c>
       <c r="U37">
-        <v>42.87716623719999</v>
+        <v>38.68527029716731</v>
       </c>
       <c r="V37">
-        <v>41.95263222920072</v>
+        <v>35.51490576988931</v>
       </c>
       <c r="W37">
-        <v>35.7390171770302</v>
+        <v>26.52613482699831</v>
       </c>
       <c r="X37">
-        <v>30.05159762861072</v>
+        <v>25.52643129346025</v>
       </c>
       <c r="Y37">
-        <v>27.44643006866399</v>
+        <v>27.93373723240262</v>
       </c>
       <c r="Z37">
-        <v>29.32732079474302</v>
+        <v>50.81505732289855</v>
       </c>
       <c r="AA37">
-        <v>27.00758469972282</v>
+        <v>26.18713472730831</v>
       </c>
       <c r="AB37">
-        <v>29.95605734040739</v>
+        <v>40.08576089779439</v>
       </c>
       <c r="AC37">
-        <v>32.25004844769783</v>
+        <v>37.9392686028002</v>
       </c>
       <c r="AD37">
-        <v>39.99558212360174</v>
+        <v>51.58783847706121</v>
       </c>
       <c r="AE37">
-        <v>42.72168903590919</v>
+        <v>40.18449039403399</v>
       </c>
       <c r="AF37">
-        <v>41.35338175220146</v>
+        <v>24.75849786655747</v>
       </c>
       <c r="AG37">
-        <v>39.07705974077889</v>
+        <v>35.64884758843076</v>
       </c>
       <c r="AH37">
-        <v>35.14811787735403</v>
+        <v>32.47848270704786</v>
       </c>
       <c r="AI37">
-        <v>35.55674807477892</v>
+        <v>23.48971150310127</v>
       </c>
       <c r="AJ37">
-        <v>36.16476347553988</v>
+        <v>22.49000842529018</v>
       </c>
       <c r="AK37">
-        <v>34.73114468932879</v>
+        <v>24.89731489951837</v>
       </c>
       <c r="AL37">
-        <v>45.59840403554063</v>
+        <v>47.77863521418584</v>
       </c>
       <c r="AM37">
-        <v>41.52785185476593</v>
+        <v>23.1507135113245</v>
       </c>
       <c r="AN37">
-        <v>41.08890266722583</v>
+        <v>37.04933982170233</v>
+      </c>
+      <c r="AO37">
+        <v>34.90284751611121</v>
+      </c>
+      <c r="AP37">
+        <v>48.55141712395631</v>
+      </c>
+      <c r="AQ37">
+        <v>37.14806835760687</v>
+      </c>
+      <c r="AR37">
+        <v>21.72207547366992</v>
+      </c>
+      <c r="AS37">
+        <v>32.61242478479173</v>
+      </c>
+      <c r="AT37">
+        <v>29.44205984946473</v>
+      </c>
+      <c r="AU37">
+        <v>20.45328880596435</v>
+      </c>
+      <c r="AV37">
+        <v>19.45358564722301</v>
+      </c>
+      <c r="AW37">
+        <v>21.86089200019215</v>
+      </c>
+      <c r="AX37">
+        <v>44.74221229632895</v>
+      </c>
+      <c r="AY37">
+        <v>20.11428989351273</v>
+      </c>
+      <c r="AZ37">
+        <v>34.01291620916062</v>
       </c>
       <c r="BA37">
-        <v>37.50868138903601</v>
+        <v>31.86642380692046</v>
       </c>
       <c r="BB37">
-        <v>35.29091565448712</v>
+        <v>45.51499361553097</v>
       </c>
       <c r="BC37">
-        <v>33.93649429788927</v>
+        <v>34.11164519524932</v>
       </c>
       <c r="BD37">
-        <v>28.61038759961211</v>
+        <v>18.68565244986874</v>
       </c>
       <c r="BE37">
-        <v>27.45828659505273</v>
+        <v>29.57600201510117</v>
       </c>
       <c r="BF37">
-        <v>27.07327764456219</v>
+        <v>26.4056372337624</v>
       </c>
       <c r="BG37">
-        <v>27.40845249960816</v>
+        <v>17.41686625135767</v>
       </c>
       <c r="BH37">
-        <v>27.46366863046304</v>
+        <v>16.41716296651449</v>
       </c>
       <c r="BI37">
-        <v>26.83888483598707</v>
+        <v>18.82446919642337</v>
       </c>
       <c r="BJ37">
-        <v>30.01702771434875</v>
+        <v>41.70578946026059</v>
       </c>
       <c r="BK37">
-        <v>28.30119301178116</v>
+        <v>17.07786706382522</v>
       </c>
       <c r="BL37">
-        <v>28.53665458167438</v>
+        <v>30.9764933725037</v>
       </c>
       <c r="BM37">
-        <v>29.66759551601768</v>
+        <v>31.86642380692046</v>
       </c>
       <c r="BN37">
-        <v>29.66759551601768</v>
+        <v>45.51499361553097</v>
       </c>
       <c r="BO37">
-        <v>29.66759551601768</v>
+        <v>34.11164519524932</v>
       </c>
       <c r="BP37">
-        <v>29.66759551601768</v>
+        <v>18.68565244986874</v>
       </c>
       <c r="BQ37">
-        <v>29.66759551601768</v>
+        <v>29.57600201510117</v>
       </c>
       <c r="BR37">
-        <v>29.66759551601768</v>
+        <v>26.4056372337624</v>
       </c>
       <c r="BS37">
-        <v>29.66759551601768</v>
+        <v>17.41686625135767</v>
       </c>
       <c r="BT37">
-        <v>29.66759551601768</v>
+        <v>16.41716296651449</v>
       </c>
       <c r="BU37">
-        <v>29.66759551601768</v>
+        <v>18.82446919642337</v>
       </c>
       <c r="BV37">
-        <v>29.66759551601768</v>
+        <v>41.70578946026059</v>
       </c>
       <c r="BW37">
-        <v>29.66759551601768</v>
+        <v>17.07786706382522</v>
       </c>
       <c r="BX37">
-        <v>29.66759551601768</v>
+        <v>30.9764933725037</v>
       </c>
       <c r="BY37">
-        <v>50.51</v>
+        <v>51.7</v>
       </c>
     </row>
   </sheetData>
